--- a/EDT_Edition.xlsx
+++ b/EDT_Edition.xlsx
@@ -805,12 +805,12 @@
     <t>TD-Élément de mécanique-G4</t>
   </si>
   <si>
+    <t>TP-Éléments de mécanique-SG31</t>
+  </si>
+  <si>
     <t>TD-Élément de mécanique-G8</t>
   </si>
   <si>
-    <t>TP-Éléments de mécanique-SG31</t>
-  </si>
-  <si>
     <t>TP-Structure de la matière-SG31</t>
   </si>
   <si>
@@ -1384,12 +1384,12 @@
     <t>TP-Programmation Python-G1A/1B</t>
   </si>
   <si>
+    <t>TP-Ondes et vibrations-G1B/1A</t>
+  </si>
+  <si>
     <t>TP-Électronique fondamentale 01-G2B/2A</t>
   </si>
   <si>
-    <t>TP-Ondes et vibrations-G1B/1A</t>
-  </si>
-  <si>
     <t>TD-Électronique fondamentale 01-G2</t>
   </si>
   <si>
@@ -2509,12 +2509,12 @@
     <t>TP-Ondes et vibrations-SG31</t>
   </si>
   <si>
+    <t>TP-Ondes et vibrations-SG32</t>
+  </si>
+  <si>
     <t>TP-Programmation Python-SG41</t>
   </si>
   <si>
-    <t>TP-Ondes et vibrations-SG32</t>
-  </si>
-  <si>
     <t>TP-Programmation Python-SG42</t>
   </si>
   <si>
@@ -2689,18 +2689,18 @@
     <t>TP-Ondes et vibrations-G4A/G4B</t>
   </si>
   <si>
+    <t>TD-Électrotechnique fondamentale-G3</t>
+  </si>
+  <si>
+    <t>TP-Électrotechnique fondamentale-G5A/G5B</t>
+  </si>
+  <si>
+    <t>TP-Électrotechnique fondamentale-G4A/G4B</t>
+  </si>
+  <si>
     <t>TP-Électronique fondamentale-G4A/4B/G03</t>
   </si>
   <si>
-    <t>TD-Électrotechnique fondamentale-G3</t>
-  </si>
-  <si>
-    <t>TP-Électrotechnique fondamentale-G5A/G5B</t>
-  </si>
-  <si>
-    <t>TP-Électrotechnique fondamentale-G4A/G4B</t>
-  </si>
-  <si>
     <t>TP-Électronique fondamentale-G2A/2B</t>
   </si>
   <si>
@@ -3961,210 +3961,210 @@
     <t>SEMMAK ABDELKADER</t>
   </si>
   <si>
+    <t>Non défini-ELT</t>
+  </si>
+  <si>
+    <t>KHIAT WALID</t>
+  </si>
+  <si>
+    <t>FELLAH MOHAMMED KARIM</t>
+  </si>
+  <si>
+    <t>BELAIDI OUAFIA</t>
+  </si>
+  <si>
+    <t>GRABA ABDELMADJID GUESSOUM</t>
+  </si>
+  <si>
+    <t>MOSTEFAOUI</t>
+  </si>
+  <si>
+    <t>ADDAD MOUAD</t>
+  </si>
+  <si>
+    <t>SEKKAL SIDI MOHAMMED</t>
+  </si>
+  <si>
+    <t>SEDDIKI ALI</t>
+  </si>
+  <si>
+    <t>FARAH MEHDI CHEMSEDDINE</t>
+  </si>
+  <si>
+    <t>DJEBBARI ALI</t>
+  </si>
+  <si>
+    <t>MAHIDDINE ABDERRAHIM</t>
+  </si>
+  <si>
+    <t>ABOURA LAMIA TOURIA</t>
+  </si>
+  <si>
+    <t>MESKINE FATIHA</t>
+  </si>
+  <si>
+    <t>BENHAMIDA FARID</t>
+  </si>
+  <si>
+    <t>JBILOU MOKHTARIA</t>
+  </si>
+  <si>
+    <t>GHAZEL FATIHA</t>
+  </si>
+  <si>
+    <t>BENDIMERAD SALAH EDDINE</t>
+  </si>
+  <si>
+    <t>MEGUEDAD ABOUBAKR</t>
+  </si>
+  <si>
+    <t>BECHEKIR SEYF EDDINE</t>
+  </si>
+  <si>
+    <t>DJELLOULI YOUNES</t>
+  </si>
+  <si>
+    <t>TOUHAMI SEDDIK</t>
+  </si>
+  <si>
+    <t>NASSOUR KAMEL</t>
+  </si>
+  <si>
+    <t>AYAD ABDELGHANI</t>
+  </si>
+  <si>
+    <t>SEMMAH ABDELHAFID</t>
+  </si>
+  <si>
+    <t>BOUBEKEUR HALIMA</t>
+  </si>
+  <si>
+    <t>MANSOURI ABDERRAZAK</t>
+  </si>
+  <si>
+    <t>ZIDI SID AHMED</t>
+  </si>
+  <si>
+    <t>HADJ BOULANOUAR RACHID</t>
+  </si>
+  <si>
+    <t>REGUIEG ZAKARIA</t>
+  </si>
+  <si>
+    <t>BOUKHOULDA FODIL</t>
+  </si>
+  <si>
+    <t>NEMMICH SAID</t>
+  </si>
+  <si>
+    <t>MEKHFI KHALIDA</t>
+  </si>
+  <si>
+    <t>REZOUG MOHAMMED</t>
+  </si>
+  <si>
+    <t>MILOUA FARID</t>
+  </si>
+  <si>
+    <t>BELLEBNA YASSINE</t>
+  </si>
+  <si>
+    <t>MAAMMAR MOHAMED</t>
+  </si>
+  <si>
+    <t>BAHLIL MOUNIR</t>
+  </si>
+  <si>
+    <t>MECHETTEM KHALIDA</t>
+  </si>
+  <si>
+    <t>BENSEDDIK NADIA</t>
+  </si>
+  <si>
+    <t>CHIRANI SOUMIA</t>
+  </si>
+  <si>
+    <t>LARBI ZIDI</t>
+  </si>
+  <si>
+    <t>DOUIAICI MOHAMED</t>
+  </si>
+  <si>
+    <t>BEDDAD BOUCIF</t>
+  </si>
+  <si>
+    <t>BELHALLOUCHE LAKHDAR</t>
+  </si>
+  <si>
+    <t>ATTAR IMAD</t>
+  </si>
+  <si>
+    <t>BENSALEM MOHAMMED MUSTAPHA</t>
+  </si>
+  <si>
+    <t>DRIEF FAIZA</t>
+  </si>
+  <si>
+    <t>BENOUAR MOHAMED</t>
+  </si>
+  <si>
+    <t>ELGHODASSE ABDEL MADJID</t>
+  </si>
+  <si>
+    <t>HAMMAR MEHDI</t>
+  </si>
+  <si>
+    <t>IKKACHE NARIMEN</t>
+  </si>
+  <si>
+    <t>SAHRAOUI HADIL</t>
+  </si>
+  <si>
+    <t>MELIANI ABDELHAK</t>
+  </si>
+  <si>
+    <t>KADRI RANIA</t>
+  </si>
+  <si>
+    <t>BOULARAF AICHA</t>
+  </si>
+  <si>
+    <t>TALEB SOUMIA</t>
+  </si>
+  <si>
+    <t>BENMESSAOUD LEYLA</t>
+  </si>
+  <si>
+    <t>SAYAH RAFIK</t>
+  </si>
+  <si>
+    <t>NON DÉFINI-AUTO</t>
+  </si>
+  <si>
+    <t>BENSAID DJILALI</t>
+  </si>
+  <si>
+    <t>BENKHALLOUK KADDOUR</t>
+  </si>
+  <si>
+    <t>MILOUDI + BOUDRAA</t>
+  </si>
+  <si>
+    <t>BENAMARA ZINEB</t>
+  </si>
+  <si>
+    <t>BENSAID DJILALI + MASSIM</t>
+  </si>
+  <si>
+    <t>MILOUDI MOHAMED</t>
+  </si>
+  <si>
+    <t>DJEHAF MOHAMMED ABDELJALIL</t>
+  </si>
+  <si>
     <t>EL-FIAD MOHAMED DJILLALI</t>
   </si>
   <si>
-    <t>KHIAT WALID</t>
-  </si>
-  <si>
-    <t>FELLAH MOHAMMED KARIM</t>
-  </si>
-  <si>
-    <t>BELAIDI OUAFIA</t>
-  </si>
-  <si>
-    <t>GRABA ABDELMADJID GUESSOUM</t>
-  </si>
-  <si>
-    <t>MOSTEFAOUI</t>
-  </si>
-  <si>
-    <t>ADDAD MOUAD</t>
-  </si>
-  <si>
-    <t>SEKKAL SIDI MOHAMMED</t>
-  </si>
-  <si>
-    <t>SEDDIKI ALI</t>
-  </si>
-  <si>
-    <t>FARAH MEHDI CHEMSEDDINE</t>
-  </si>
-  <si>
-    <t>DJEBBARI ALI</t>
-  </si>
-  <si>
-    <t>MAHIDDINE ABDERRAHIM</t>
-  </si>
-  <si>
-    <t>ABOURA LAMIA TOURIA</t>
-  </si>
-  <si>
-    <t>MESKINE FATIHA</t>
-  </si>
-  <si>
-    <t>BENHAMIDA FARID</t>
-  </si>
-  <si>
-    <t>JBILOU MOKHTARIA</t>
-  </si>
-  <si>
-    <t>GHAZEL FATIHA</t>
-  </si>
-  <si>
-    <t>Non défini-ELT</t>
-  </si>
-  <si>
-    <t>BENDIMERAD SALAH EDDINE</t>
-  </si>
-  <si>
-    <t>MEGUEDAD ABOUBAKR</t>
-  </si>
-  <si>
-    <t>BECHEKIR SEYF EDDINE</t>
-  </si>
-  <si>
-    <t>DJELLOULI YOUNES</t>
-  </si>
-  <si>
-    <t>TOUHAMI SEDDIK</t>
-  </si>
-  <si>
-    <t>NASSOUR KAMEL</t>
-  </si>
-  <si>
-    <t>AYAD ABDELGHANI</t>
-  </si>
-  <si>
-    <t>SEMMAH ABDELHAFID</t>
-  </si>
-  <si>
-    <t>BOUBEKEUR HALIMA</t>
-  </si>
-  <si>
-    <t>MANSOURI ABDERRAZAK</t>
-  </si>
-  <si>
-    <t>ZIDI SID AHMED</t>
-  </si>
-  <si>
-    <t>HADJ BOULANOUAR RACHID</t>
-  </si>
-  <si>
-    <t>REGUIEG ZAKARIA</t>
-  </si>
-  <si>
-    <t>BOUKHOULDA FODIL</t>
-  </si>
-  <si>
-    <t>NEMMICH SAID</t>
-  </si>
-  <si>
-    <t>MEKHFI KHALIDA</t>
-  </si>
-  <si>
-    <t>REZOUG MOHAMMED</t>
-  </si>
-  <si>
-    <t>MILOUA FARID</t>
-  </si>
-  <si>
-    <t>BELLEBNA YASSINE</t>
-  </si>
-  <si>
-    <t>MAAMMAR MOHAMED</t>
-  </si>
-  <si>
-    <t>BAHLIL MOUNIR</t>
-  </si>
-  <si>
-    <t>MECHETTEM KHALIDA</t>
-  </si>
-  <si>
-    <t>BENSEDDIK NADIA</t>
-  </si>
-  <si>
-    <t>CHIRANI SOUMIA</t>
-  </si>
-  <si>
-    <t>LARBI ZIDI</t>
-  </si>
-  <si>
-    <t>DOUIAICI MOHAMED</t>
-  </si>
-  <si>
-    <t>BEDDAD BOUCIF</t>
-  </si>
-  <si>
-    <t>BELHALLOUCHE LAKHDAR</t>
-  </si>
-  <si>
-    <t>ATTAR IMAD</t>
-  </si>
-  <si>
-    <t>BENSALEM MOHAMMED MUSTAPHA</t>
-  </si>
-  <si>
-    <t>DRIEF FAIZA</t>
-  </si>
-  <si>
-    <t>BENOUAR MOHAMED</t>
-  </si>
-  <si>
-    <t>ELGHODASSE ABDEL MADJID</t>
-  </si>
-  <si>
-    <t>HAMMAR MEHDI</t>
-  </si>
-  <si>
-    <t>IKKACHE NARIMEN</t>
-  </si>
-  <si>
-    <t>SAHRAOUI HADIL</t>
-  </si>
-  <si>
-    <t>MELIANI ABDELHAK</t>
-  </si>
-  <si>
-    <t>KADRI RANIA</t>
-  </si>
-  <si>
-    <t>BOULARAF AICHA</t>
-  </si>
-  <si>
-    <t>TALEB SOUMIA</t>
-  </si>
-  <si>
-    <t>BENMESSAOUD LEYLA</t>
-  </si>
-  <si>
-    <t>SAYAH RAFIK</t>
-  </si>
-  <si>
-    <t>NON DÉFINI-AUTO</t>
-  </si>
-  <si>
-    <t>BENSAID DJILALI</t>
-  </si>
-  <si>
-    <t>BENKHALLOUK KADDOUR</t>
-  </si>
-  <si>
-    <t>MILOUDI + BOUDRAA</t>
-  </si>
-  <si>
-    <t>BENAMARA ZINEB</t>
-  </si>
-  <si>
-    <t>BENSAID DJILALI + MASSIM</t>
-  </si>
-  <si>
-    <t>MILOUDI MOHAMED</t>
-  </si>
-  <si>
-    <t>DJEHAF MOHAMMED ABDELJALIL</t>
-  </si>
-  <si>
     <t>MEDLES IMED</t>
   </si>
   <si>
@@ -4222,7 +4222,7 @@
     <t>OUARI KHEIRA + BERRAHAL BELABBES</t>
   </si>
   <si>
-    <t>TOLBI BILAL + HASSANI NAIMA</t>
+    <t>TOLBI BILAL + HASSANI YOUCEF</t>
   </si>
   <si>
     <t>OUKLI MIMOUNA</t>
@@ -4297,12 +4297,12 @@
     <t>BENYEKHLEF SOUAD</t>
   </si>
   <si>
+    <t>DR.A.BELASRI</t>
+  </si>
+  <si>
     <t>BOUZIDI ATTOUYA / BENSAAD ZOUAOUI</t>
   </si>
   <si>
-    <t>DR.A.BELASRI</t>
-  </si>
-  <si>
     <t>DR. A. BENKETLAN</t>
   </si>
   <si>
@@ -4783,18 +4783,18 @@
     <t>DRE.K.EZZINE / DR. L MEKHLEF</t>
   </si>
   <si>
+    <t>DR.HAMBI</t>
+  </si>
+  <si>
+    <t>DRE. M. DEKMOUS / DRE. M. HAMBI</t>
+  </si>
+  <si>
+    <t>DRE.M. HAMBI / DR.ZAREB</t>
+  </si>
+  <si>
     <t>BENSAAD ZOUAOUI / PRE.BOUZIDI 33 MME D. BENSIDI AHMED</t>
   </si>
   <si>
-    <t>DR.HAMBI</t>
-  </si>
-  <si>
-    <t>DRE. M. DEKMOUS / DRE. M. HAMBI</t>
-  </si>
-  <si>
-    <t>DRE.M. HAMBI / DR.ZAREB</t>
-  </si>
-  <si>
     <t>TURKI</t>
   </si>
   <si>
@@ -5209,12 +5209,12 @@
     <t>Info 01</t>
   </si>
   <si>
+    <t>Lab B05</t>
+  </si>
+  <si>
     <t>Lab B08</t>
   </si>
   <si>
-    <t>Lab B05</t>
-  </si>
-  <si>
     <t>BS08</t>
   </si>
   <si>
@@ -5374,10 +5374,10 @@
     <t>Lab OV Bloc B5</t>
   </si>
   <si>
+    <t>BS16</t>
+  </si>
+  <si>
     <t>Lab B16 / BS03</t>
-  </si>
-  <si>
-    <t>BS16</t>
   </si>
   <si>
     <t>Salle de TP Systèmes Asservis</t>
@@ -12937,7 +12937,7 @@
         <v>959</v>
       </c>
       <c r="C272" t="s">
-        <v>1332</v>
+        <v>1315</v>
       </c>
       <c r="D272" t="s">
         <v>1612</v>
@@ -12989,7 +12989,7 @@
         <v>959</v>
       </c>
       <c r="C274" t="s">
-        <v>1332</v>
+        <v>1315</v>
       </c>
       <c r="D274" t="s">
         <v>1616</v>
@@ -13015,7 +13015,7 @@
         <v>958</v>
       </c>
       <c r="C275" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D275" t="s">
         <v>1612</v>
@@ -13067,7 +13067,7 @@
         <v>978</v>
       </c>
       <c r="C277" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D277" t="s">
         <v>1622</v>
@@ -13119,7 +13119,7 @@
         <v>961</v>
       </c>
       <c r="C279" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="D279" t="s">
         <v>1615</v>
@@ -13145,7 +13145,7 @@
         <v>961</v>
       </c>
       <c r="C280" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="D280" t="s">
         <v>1616</v>
@@ -13249,7 +13249,7 @@
         <v>959</v>
       </c>
       <c r="C284" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D284" t="s">
         <v>1612</v>
@@ -13275,7 +13275,7 @@
         <v>959</v>
       </c>
       <c r="C285" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D285" t="s">
         <v>1612</v>
@@ -13301,7 +13301,7 @@
         <v>959</v>
       </c>
       <c r="C286" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="D286" t="s">
         <v>1613</v>
@@ -13353,7 +13353,7 @@
         <v>959</v>
       </c>
       <c r="C288" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="D288" t="s">
         <v>1614</v>
@@ -13405,7 +13405,7 @@
         <v>958</v>
       </c>
       <c r="C290" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D290" t="s">
         <v>1615</v>
@@ -13431,7 +13431,7 @@
         <v>959</v>
       </c>
       <c r="C291" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D291" t="s">
         <v>1616</v>
@@ -13457,7 +13457,7 @@
         <v>959</v>
       </c>
       <c r="C292" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D292" t="s">
         <v>1616</v>
@@ -13561,7 +13561,7 @@
         <v>958</v>
       </c>
       <c r="C296" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D296" t="s">
         <v>1615</v>
@@ -13613,7 +13613,7 @@
         <v>982</v>
       </c>
       <c r="C298" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D298" t="s">
         <v>1619</v>
@@ -13639,7 +13639,7 @@
         <v>983</v>
       </c>
       <c r="C299" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D299" t="s">
         <v>1619</v>
@@ -13665,7 +13665,7 @@
         <v>982</v>
       </c>
       <c r="C300" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D300" t="s">
         <v>1620</v>
@@ -13691,7 +13691,7 @@
         <v>983</v>
       </c>
       <c r="C301" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D301" t="s">
         <v>1620</v>
@@ -13717,7 +13717,7 @@
         <v>984</v>
       </c>
       <c r="C302" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D302" t="s">
         <v>1617</v>
@@ -13795,7 +13795,7 @@
         <v>985</v>
       </c>
       <c r="C305" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D305" t="s">
         <v>1619</v>
@@ -13821,7 +13821,7 @@
         <v>958</v>
       </c>
       <c r="C306" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D306" t="s">
         <v>1616</v>
@@ -13847,7 +13847,7 @@
         <v>961</v>
       </c>
       <c r="C307" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D307" t="s">
         <v>1612</v>
@@ -13873,7 +13873,7 @@
         <v>958</v>
       </c>
       <c r="C308" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="D308" t="s">
         <v>1615</v>
@@ -13899,7 +13899,7 @@
         <v>986</v>
       </c>
       <c r="C309" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D309" t="s">
         <v>1620</v>
@@ -13925,7 +13925,7 @@
         <v>959</v>
       </c>
       <c r="C310" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D310" t="s">
         <v>1612</v>
@@ -13951,7 +13951,7 @@
         <v>959</v>
       </c>
       <c r="C311" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D311" t="s">
         <v>1618</v>
@@ -13977,7 +13977,7 @@
         <v>959</v>
       </c>
       <c r="C312" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D312" t="s">
         <v>1613</v>
@@ -14003,7 +14003,7 @@
         <v>959</v>
       </c>
       <c r="C313" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D313" t="s">
         <v>1614</v>
@@ -14029,7 +14029,7 @@
         <v>987</v>
       </c>
       <c r="C314" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D314" t="s">
         <v>1619</v>
@@ -14055,7 +14055,7 @@
         <v>961</v>
       </c>
       <c r="C315" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D315" t="s">
         <v>1616</v>
@@ -14081,7 +14081,7 @@
         <v>959</v>
       </c>
       <c r="C316" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D316" t="s">
         <v>1612</v>
@@ -14159,7 +14159,7 @@
         <v>961</v>
       </c>
       <c r="C319" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D319" t="s">
         <v>1615</v>
@@ -14185,7 +14185,7 @@
         <v>958</v>
       </c>
       <c r="C320" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D320" t="s">
         <v>1616</v>
@@ -14211,7 +14211,7 @@
         <v>958</v>
       </c>
       <c r="C321" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D321" t="s">
         <v>1616</v>
@@ -14237,7 +14237,7 @@
         <v>961</v>
       </c>
       <c r="C322" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D322" t="s">
         <v>1612</v>
@@ -14263,7 +14263,7 @@
         <v>958</v>
       </c>
       <c r="C323" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D323" t="s">
         <v>1613</v>
@@ -14289,7 +14289,7 @@
         <v>961</v>
       </c>
       <c r="C324" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D324" t="s">
         <v>1614</v>
@@ -14315,7 +14315,7 @@
         <v>959</v>
       </c>
       <c r="C325" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D325" t="s">
         <v>1615</v>
@@ -14341,7 +14341,7 @@
         <v>958</v>
       </c>
       <c r="C326" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D326" t="s">
         <v>1616</v>
@@ -14367,7 +14367,7 @@
         <v>961</v>
       </c>
       <c r="C327" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D327" t="s">
         <v>1612</v>
@@ -14393,7 +14393,7 @@
         <v>959</v>
       </c>
       <c r="C328" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D328" t="s">
         <v>1613</v>
@@ -14419,7 +14419,7 @@
         <v>958</v>
       </c>
       <c r="C329" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D329" t="s">
         <v>1614</v>
@@ -14445,7 +14445,7 @@
         <v>958</v>
       </c>
       <c r="C330" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D330" t="s">
         <v>1615</v>
@@ -14471,7 +14471,7 @@
         <v>958</v>
       </c>
       <c r="C331" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D331" t="s">
         <v>1616</v>
@@ -14497,7 +14497,7 @@
         <v>958</v>
       </c>
       <c r="C332" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D332" t="s">
         <v>1612</v>
@@ -14523,7 +14523,7 @@
         <v>959</v>
       </c>
       <c r="C333" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D333" t="s">
         <v>1613</v>
@@ -14601,7 +14601,7 @@
         <v>988</v>
       </c>
       <c r="C336" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D336" t="s">
         <v>1612</v>
@@ -14627,7 +14627,7 @@
         <v>989</v>
       </c>
       <c r="C337" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D337" t="s">
         <v>1612</v>
@@ -14653,7 +14653,7 @@
         <v>959</v>
       </c>
       <c r="C338" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D338" t="s">
         <v>1612</v>
@@ -14731,7 +14731,7 @@
         <v>988</v>
       </c>
       <c r="C341" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D341" t="s">
         <v>1618</v>
@@ -14757,7 +14757,7 @@
         <v>989</v>
       </c>
       <c r="C342" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D342" t="s">
         <v>1618</v>
@@ -14783,7 +14783,7 @@
         <v>959</v>
       </c>
       <c r="C343" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D343" t="s">
         <v>1618</v>
@@ -14861,7 +14861,7 @@
         <v>988</v>
       </c>
       <c r="C346" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D346" t="s">
         <v>1613</v>
@@ -14887,7 +14887,7 @@
         <v>959</v>
       </c>
       <c r="C347" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D347" t="s">
         <v>1613</v>
@@ -14913,7 +14913,7 @@
         <v>989</v>
       </c>
       <c r="C348" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D348" t="s">
         <v>1613</v>
@@ -14939,7 +14939,7 @@
         <v>959</v>
       </c>
       <c r="C349" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D349" t="s">
         <v>1613</v>
@@ -14965,7 +14965,7 @@
         <v>988</v>
       </c>
       <c r="C350" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D350" t="s">
         <v>1614</v>
@@ -14991,7 +14991,7 @@
         <v>959</v>
       </c>
       <c r="C351" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D351" t="s">
         <v>1614</v>
@@ -15017,7 +15017,7 @@
         <v>989</v>
       </c>
       <c r="C352" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D352" t="s">
         <v>1614</v>
@@ -15043,7 +15043,7 @@
         <v>959</v>
       </c>
       <c r="C353" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D353" t="s">
         <v>1614</v>
@@ -15069,7 +15069,7 @@
         <v>958</v>
       </c>
       <c r="C354" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D354" t="s">
         <v>1615</v>
@@ -15121,7 +15121,7 @@
         <v>990</v>
       </c>
       <c r="C356" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D356" t="s">
         <v>1616</v>
@@ -15173,7 +15173,7 @@
         <v>991</v>
       </c>
       <c r="C358" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D358" t="s">
         <v>1612</v>
@@ -15199,7 +15199,7 @@
         <v>991</v>
       </c>
       <c r="C359" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D359" t="s">
         <v>1618</v>
@@ -15225,7 +15225,7 @@
         <v>959</v>
       </c>
       <c r="C360" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D360" t="s">
         <v>1613</v>
@@ -15248,7 +15248,7 @@
         <v>263</v>
       </c>
       <c r="B361" t="s">
-        <v>991</v>
+        <v>959</v>
       </c>
       <c r="C361" t="s">
         <v>1357</v>
@@ -15260,7 +15260,7 @@
         <v>1639</v>
       </c>
       <c r="F361" t="s">
-        <v>1640</v>
+        <v>1647</v>
       </c>
       <c r="G361" t="s">
         <v>1800</v>
@@ -15274,10 +15274,10 @@
         <v>264</v>
       </c>
       <c r="B362" t="s">
-        <v>959</v>
+        <v>991</v>
       </c>
       <c r="C362" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="D362" t="s">
         <v>1613</v>
@@ -15286,7 +15286,7 @@
         <v>1639</v>
       </c>
       <c r="F362" t="s">
-        <v>1647</v>
+        <v>1640</v>
       </c>
       <c r="G362" t="s">
         <v>1800</v>
@@ -15303,7 +15303,7 @@
         <v>959</v>
       </c>
       <c r="C363" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D363" t="s">
         <v>1614</v>
@@ -15323,10 +15323,10 @@
     </row>
     <row r="364" spans="1:8">
       <c r="A364" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B364" t="s">
-        <v>991</v>
+        <v>959</v>
       </c>
       <c r="C364" t="s">
         <v>1357</v>
@@ -15338,7 +15338,7 @@
         <v>1639</v>
       </c>
       <c r="F364" t="s">
-        <v>1640</v>
+        <v>1647</v>
       </c>
       <c r="G364" t="s">
         <v>1800</v>
@@ -15349,13 +15349,13 @@
     </row>
     <row r="365" spans="1:8">
       <c r="A365" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B365" t="s">
-        <v>959</v>
+        <v>991</v>
       </c>
       <c r="C365" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="D365" t="s">
         <v>1614</v>
@@ -15364,7 +15364,7 @@
         <v>1639</v>
       </c>
       <c r="F365" t="s">
-        <v>1647</v>
+        <v>1640</v>
       </c>
       <c r="G365" t="s">
         <v>1800</v>
@@ -15433,7 +15433,7 @@
         <v>959</v>
       </c>
       <c r="C368" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D368" t="s">
         <v>1623</v>
@@ -15459,7 +15459,7 @@
         <v>959</v>
       </c>
       <c r="C369" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D369" t="s">
         <v>1623</v>
@@ -15485,7 +15485,7 @@
         <v>959</v>
       </c>
       <c r="C370" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D370" t="s">
         <v>1624</v>
@@ -15511,7 +15511,7 @@
         <v>961</v>
       </c>
       <c r="C371" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D371" t="s">
         <v>1612</v>
@@ -15537,7 +15537,7 @@
         <v>961</v>
       </c>
       <c r="C372" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D372" t="s">
         <v>1612</v>
@@ -15563,7 +15563,7 @@
         <v>961</v>
       </c>
       <c r="C373" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D373" t="s">
         <v>1612</v>
@@ -15589,7 +15589,7 @@
         <v>959</v>
       </c>
       <c r="C374" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D374" t="s">
         <v>1625</v>
@@ -15615,7 +15615,7 @@
         <v>959</v>
       </c>
       <c r="C375" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D375" t="s">
         <v>1625</v>
@@ -15641,7 +15641,7 @@
         <v>961</v>
       </c>
       <c r="C376" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D376" t="s">
         <v>1618</v>
@@ -15667,7 +15667,7 @@
         <v>961</v>
       </c>
       <c r="C377" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D377" t="s">
         <v>1618</v>
@@ -15693,7 +15693,7 @@
         <v>959</v>
       </c>
       <c r="C378" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D378" t="s">
         <v>1626</v>
@@ -15719,7 +15719,7 @@
         <v>959</v>
       </c>
       <c r="C379" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D379" t="s">
         <v>1626</v>
@@ -15745,7 +15745,7 @@
         <v>961</v>
       </c>
       <c r="C380" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D380" t="s">
         <v>1613</v>
@@ -15771,7 +15771,7 @@
         <v>961</v>
       </c>
       <c r="C381" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D381" t="s">
         <v>1613</v>
@@ -15797,7 +15797,7 @@
         <v>961</v>
       </c>
       <c r="C382" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="D382" t="s">
         <v>1613</v>
@@ -15823,7 +15823,7 @@
         <v>959</v>
       </c>
       <c r="C383" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D383" t="s">
         <v>1613</v>
@@ -15849,7 +15849,7 @@
         <v>961</v>
       </c>
       <c r="C384" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D384" t="s">
         <v>1613</v>
@@ -15875,7 +15875,7 @@
         <v>992</v>
       </c>
       <c r="C385" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D385" t="s">
         <v>1613</v>
@@ -15901,7 +15901,7 @@
         <v>988</v>
       </c>
       <c r="C386" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D386" t="s">
         <v>1614</v>
@@ -15927,7 +15927,7 @@
         <v>961</v>
       </c>
       <c r="C387" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D387" t="s">
         <v>1614</v>
@@ -15953,7 +15953,7 @@
         <v>961</v>
       </c>
       <c r="C388" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="D388" t="s">
         <v>1614</v>
@@ -15979,7 +15979,7 @@
         <v>959</v>
       </c>
       <c r="C389" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D389" t="s">
         <v>1614</v>
@@ -16005,7 +16005,7 @@
         <v>992</v>
       </c>
       <c r="C390" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D390" t="s">
         <v>1614</v>
@@ -16031,7 +16031,7 @@
         <v>959</v>
       </c>
       <c r="C391" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D391" t="s">
         <v>1627</v>
@@ -16057,7 +16057,7 @@
         <v>959</v>
       </c>
       <c r="C392" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="D392" t="s">
         <v>1627</v>
@@ -16083,7 +16083,7 @@
         <v>961</v>
       </c>
       <c r="C393" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D393" t="s">
         <v>1615</v>
@@ -16109,7 +16109,7 @@
         <v>959</v>
       </c>
       <c r="C394" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D394" t="s">
         <v>1615</v>
@@ -16135,7 +16135,7 @@
         <v>959</v>
       </c>
       <c r="C395" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D395" t="s">
         <v>1628</v>
@@ -16161,7 +16161,7 @@
         <v>959</v>
       </c>
       <c r="C396" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D396" t="s">
         <v>1628</v>
@@ -16187,7 +16187,7 @@
         <v>959</v>
       </c>
       <c r="C397" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="D397" t="s">
         <v>1628</v>
@@ -16213,7 +16213,7 @@
         <v>991</v>
       </c>
       <c r="C398" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D398" t="s">
         <v>1616</v>
@@ -16239,7 +16239,7 @@
         <v>959</v>
       </c>
       <c r="C399" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D399" t="s">
         <v>1616</v>
@@ -16291,7 +16291,7 @@
         <v>959</v>
       </c>
       <c r="C401" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D401" t="s">
         <v>1624</v>
@@ -16317,7 +16317,7 @@
         <v>988</v>
       </c>
       <c r="C402" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D402" t="s">
         <v>1612</v>
@@ -16343,7 +16343,7 @@
         <v>991</v>
       </c>
       <c r="C403" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D403" t="s">
         <v>1612</v>
@@ -16421,7 +16421,7 @@
         <v>959</v>
       </c>
       <c r="C406" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D406" t="s">
         <v>1625</v>
@@ -16447,7 +16447,7 @@
         <v>961</v>
       </c>
       <c r="C407" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D407" t="s">
         <v>1618</v>
@@ -16473,7 +16473,7 @@
         <v>988</v>
       </c>
       <c r="C408" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D408" t="s">
         <v>1618</v>
@@ -16499,7 +16499,7 @@
         <v>991</v>
       </c>
       <c r="C409" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D409" t="s">
         <v>1618</v>
@@ -16525,7 +16525,7 @@
         <v>961</v>
       </c>
       <c r="C410" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D410" t="s">
         <v>1618</v>
@@ -16551,7 +16551,7 @@
         <v>988</v>
       </c>
       <c r="C411" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D411" t="s">
         <v>1613</v>
@@ -16577,7 +16577,7 @@
         <v>959</v>
       </c>
       <c r="C412" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D412" t="s">
         <v>1613</v>
@@ -16603,7 +16603,7 @@
         <v>991</v>
       </c>
       <c r="C413" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D413" t="s">
         <v>1613</v>
@@ -16655,7 +16655,7 @@
         <v>992</v>
       </c>
       <c r="C415" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D415" t="s">
         <v>1613</v>
@@ -16707,7 +16707,7 @@
         <v>988</v>
       </c>
       <c r="C417" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D417" t="s">
         <v>1614</v>
@@ -16733,7 +16733,7 @@
         <v>959</v>
       </c>
       <c r="C418" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D418" t="s">
         <v>1614</v>
@@ -16759,7 +16759,7 @@
         <v>991</v>
       </c>
       <c r="C419" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D419" t="s">
         <v>1614</v>
@@ -16785,7 +16785,7 @@
         <v>961</v>
       </c>
       <c r="C420" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D420" t="s">
         <v>1614</v>
@@ -16811,7 +16811,7 @@
         <v>992</v>
       </c>
       <c r="C421" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D421" t="s">
         <v>1614</v>
@@ -16863,7 +16863,7 @@
         <v>958</v>
       </c>
       <c r="C423" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D423" t="s">
         <v>1615</v>
@@ -16889,7 +16889,7 @@
         <v>958</v>
       </c>
       <c r="C424" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D424" t="s">
         <v>1615</v>
@@ -16915,7 +16915,7 @@
         <v>990</v>
       </c>
       <c r="C425" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D425" t="s">
         <v>1616</v>
@@ -16941,7 +16941,7 @@
         <v>993</v>
       </c>
       <c r="C426" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D426" t="s">
         <v>1616</v>
@@ -16993,7 +16993,7 @@
         <v>961</v>
       </c>
       <c r="C428" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D428" t="s">
         <v>1612</v>
@@ -17019,7 +17019,7 @@
         <v>959</v>
       </c>
       <c r="C429" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D429" t="s">
         <v>1612</v>
@@ -17045,7 +17045,7 @@
         <v>959</v>
       </c>
       <c r="C430" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D430" t="s">
         <v>1612</v>
@@ -17071,7 +17071,7 @@
         <v>959</v>
       </c>
       <c r="C431" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D431" t="s">
         <v>1612</v>
@@ -17123,7 +17123,7 @@
         <v>961</v>
       </c>
       <c r="C433" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D433" t="s">
         <v>1618</v>
@@ -17149,7 +17149,7 @@
         <v>959</v>
       </c>
       <c r="C434" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D434" t="s">
         <v>1618</v>
@@ -17175,7 +17175,7 @@
         <v>959</v>
       </c>
       <c r="C435" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D435" t="s">
         <v>1618</v>
@@ -17201,7 +17201,7 @@
         <v>959</v>
       </c>
       <c r="C436" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D436" t="s">
         <v>1618</v>
@@ -17253,7 +17253,7 @@
         <v>961</v>
       </c>
       <c r="C438" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D438" t="s">
         <v>1613</v>
@@ -17279,7 +17279,7 @@
         <v>961</v>
       </c>
       <c r="C439" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D439" t="s">
         <v>1613</v>
@@ -17357,7 +17357,7 @@
         <v>961</v>
       </c>
       <c r="C442" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="D442" t="s">
         <v>1615</v>
@@ -17383,7 +17383,7 @@
         <v>961</v>
       </c>
       <c r="C443" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D443" t="s">
         <v>1615</v>
@@ -17409,7 +17409,7 @@
         <v>996</v>
       </c>
       <c r="C444" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D444" t="s">
         <v>1615</v>
@@ -17487,7 +17487,7 @@
         <v>961</v>
       </c>
       <c r="C447" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="D447" t="s">
         <v>1616</v>
@@ -17513,7 +17513,7 @@
         <v>961</v>
       </c>
       <c r="C448" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D448" t="s">
         <v>1616</v>
@@ -17539,7 +17539,7 @@
         <v>996</v>
       </c>
       <c r="C449" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D449" t="s">
         <v>1616</v>
@@ -17617,7 +17617,7 @@
         <v>998</v>
       </c>
       <c r="C452" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D452" t="s">
         <v>1615</v>
@@ -17643,7 +17643,7 @@
         <v>999</v>
       </c>
       <c r="C453" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D453" t="s">
         <v>1616</v>
@@ -17669,7 +17669,7 @@
         <v>1000</v>
       </c>
       <c r="C454" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D454" t="s">
         <v>1612</v>
@@ -17695,7 +17695,7 @@
         <v>1001</v>
       </c>
       <c r="C455" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D455" t="s">
         <v>1615</v>
@@ -17721,7 +17721,7 @@
         <v>1000</v>
       </c>
       <c r="C456" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D456" t="s">
         <v>1616</v>
@@ -17773,7 +17773,7 @@
         <v>1003</v>
       </c>
       <c r="C458" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D458" t="s">
         <v>1613</v>
@@ -17799,7 +17799,7 @@
         <v>1004</v>
       </c>
       <c r="C459" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D459" t="s">
         <v>1614</v>
@@ -17851,7 +17851,7 @@
         <v>1006</v>
       </c>
       <c r="C461" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D461" t="s">
         <v>1612</v>
@@ -17877,7 +17877,7 @@
         <v>1007</v>
       </c>
       <c r="C462" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D462" t="s">
         <v>1612</v>
@@ -17929,7 +17929,7 @@
         <v>1008</v>
       </c>
       <c r="C464" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D464" t="s">
         <v>1613</v>
@@ -17955,7 +17955,7 @@
         <v>1009</v>
       </c>
       <c r="C465" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D465" t="s">
         <v>1614</v>
@@ -18085,7 +18085,7 @@
         <v>1011</v>
       </c>
       <c r="C470" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D470" t="s">
         <v>1629</v>
@@ -18111,7 +18111,7 @@
         <v>1012</v>
       </c>
       <c r="C471" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D471" t="s">
         <v>1615</v>
@@ -18137,7 +18137,7 @@
         <v>1013</v>
       </c>
       <c r="C472" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D472" t="s">
         <v>1616</v>
@@ -18189,7 +18189,7 @@
         <v>1015</v>
       </c>
       <c r="C474" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D474" t="s">
         <v>1613</v>
@@ -18215,7 +18215,7 @@
         <v>1015</v>
       </c>
       <c r="C475" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D475" t="s">
         <v>1614</v>
@@ -18241,7 +18241,7 @@
         <v>1016</v>
       </c>
       <c r="C476" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D476" t="s">
         <v>1615</v>
@@ -18267,7 +18267,7 @@
         <v>1017</v>
       </c>
       <c r="C477" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D477" t="s">
         <v>1616</v>
@@ -18293,7 +18293,7 @@
         <v>1018</v>
       </c>
       <c r="C478" t="s">
-        <v>1315</v>
+        <v>1382</v>
       </c>
       <c r="D478" t="s">
         <v>1612</v>
@@ -18319,7 +18319,7 @@
         <v>1019</v>
       </c>
       <c r="C479" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D479" t="s">
         <v>1618</v>
@@ -18345,7 +18345,7 @@
         <v>1020</v>
       </c>
       <c r="C480" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D480" t="s">
         <v>1618</v>
@@ -18371,7 +18371,7 @@
         <v>1021</v>
       </c>
       <c r="C481" t="s">
-        <v>1315</v>
+        <v>1382</v>
       </c>
       <c r="D481" t="s">
         <v>1615</v>
@@ -18397,7 +18397,7 @@
         <v>1018</v>
       </c>
       <c r="C482" t="s">
-        <v>1315</v>
+        <v>1382</v>
       </c>
       <c r="D482" t="s">
         <v>1616</v>
@@ -18449,7 +18449,7 @@
         <v>1023</v>
       </c>
       <c r="C484" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D484" t="s">
         <v>1613</v>
@@ -18475,7 +18475,7 @@
         <v>1024</v>
       </c>
       <c r="C485" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D485" t="s">
         <v>1614</v>
@@ -18631,7 +18631,7 @@
         <v>1027</v>
       </c>
       <c r="C491" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D491" t="s">
         <v>1613</v>
@@ -18657,7 +18657,7 @@
         <v>1028</v>
       </c>
       <c r="C492" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D492" t="s">
         <v>1614</v>
@@ -18683,7 +18683,7 @@
         <v>1029</v>
       </c>
       <c r="C493" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D493" t="s">
         <v>1615</v>
@@ -18709,7 +18709,7 @@
         <v>1030</v>
       </c>
       <c r="C494" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D494" t="s">
         <v>1616</v>
@@ -18735,7 +18735,7 @@
         <v>1031</v>
       </c>
       <c r="C495" t="s">
-        <v>1332</v>
+        <v>1308</v>
       </c>
       <c r="D495" t="s">
         <v>1612</v>
@@ -18761,7 +18761,7 @@
         <v>1031</v>
       </c>
       <c r="C496" t="s">
-        <v>1332</v>
+        <v>1308</v>
       </c>
       <c r="D496" t="s">
         <v>1612</v>
@@ -18839,7 +18839,7 @@
         <v>961</v>
       </c>
       <c r="C499" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D499" t="s">
         <v>1614</v>
@@ -19307,7 +19307,7 @@
         <v>958</v>
       </c>
       <c r="C517" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D517" t="s">
         <v>1612</v>
@@ -19333,7 +19333,7 @@
         <v>961</v>
       </c>
       <c r="C518" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D518" t="s">
         <v>1613</v>
@@ -19359,7 +19359,7 @@
         <v>961</v>
       </c>
       <c r="C519" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D519" t="s">
         <v>1614</v>
@@ -19385,7 +19385,7 @@
         <v>1031</v>
       </c>
       <c r="C520" t="s">
-        <v>1332</v>
+        <v>1308</v>
       </c>
       <c r="D520" t="s">
         <v>1615</v>
@@ -19411,7 +19411,7 @@
         <v>1031</v>
       </c>
       <c r="C521" t="s">
-        <v>1332</v>
+        <v>1308</v>
       </c>
       <c r="D521" t="s">
         <v>1615</v>
@@ -19567,7 +19567,7 @@
         <v>961</v>
       </c>
       <c r="C527" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D527" t="s">
         <v>1614</v>
@@ -20347,7 +20347,7 @@
         <v>958</v>
       </c>
       <c r="C557" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D557" t="s">
         <v>1612</v>
@@ -20789,7 +20789,7 @@
         <v>1043</v>
       </c>
       <c r="C574" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D574" t="s">
         <v>1612</v>
@@ -21127,7 +21127,7 @@
         <v>1054</v>
       </c>
       <c r="C587" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D587" t="s">
         <v>1612</v>
@@ -21153,7 +21153,7 @@
         <v>1055</v>
       </c>
       <c r="C588" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D588" t="s">
         <v>1615</v>
@@ -21179,7 +21179,7 @@
         <v>1056</v>
       </c>
       <c r="C589" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D589" t="s">
         <v>1616</v>
@@ -21231,7 +21231,7 @@
         <v>1058</v>
       </c>
       <c r="C591" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D591" t="s">
         <v>1612</v>
@@ -21309,7 +21309,7 @@
         <v>1058</v>
       </c>
       <c r="C594" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D594" t="s">
         <v>1616</v>
@@ -21439,7 +21439,7 @@
         <v>1064</v>
       </c>
       <c r="C599" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D599" t="s">
         <v>1612</v>
@@ -21621,7 +21621,7 @@
         <v>1064</v>
       </c>
       <c r="C606" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D606" t="s">
         <v>1616</v>
@@ -21699,7 +21699,7 @@
         <v>1068</v>
       </c>
       <c r="C609" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D609" t="s">
         <v>1612</v>
@@ -21751,7 +21751,7 @@
         <v>1070</v>
       </c>
       <c r="C611" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D611" t="s">
         <v>1616</v>
@@ -21777,7 +21777,7 @@
         <v>961</v>
       </c>
       <c r="C612" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D612" t="s">
         <v>1612</v>
@@ -21803,7 +21803,7 @@
         <v>961</v>
       </c>
       <c r="C613" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D613" t="s">
         <v>1612</v>
@@ -21907,7 +21907,7 @@
         <v>959</v>
       </c>
       <c r="C617" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D617" t="s">
         <v>1613</v>
@@ -22063,7 +22063,7 @@
         <v>958</v>
       </c>
       <c r="C623" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D623" t="s">
         <v>1615</v>
@@ -22141,7 +22141,7 @@
         <v>961</v>
       </c>
       <c r="C626" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D626" t="s">
         <v>1616</v>
@@ -22167,7 +22167,7 @@
         <v>961</v>
       </c>
       <c r="C627" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D627" t="s">
         <v>1612</v>
@@ -22271,7 +22271,7 @@
         <v>958</v>
       </c>
       <c r="C631" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D631" t="s">
         <v>1615</v>
@@ -22505,7 +22505,7 @@
         <v>959</v>
       </c>
       <c r="C640" t="s">
-        <v>1332</v>
+        <v>1315</v>
       </c>
       <c r="D640" t="s">
         <v>1614</v>
@@ -22583,7 +22583,7 @@
         <v>958</v>
       </c>
       <c r="C643" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D643" t="s">
         <v>1612</v>
@@ -22661,7 +22661,7 @@
         <v>959</v>
       </c>
       <c r="C646" t="s">
-        <v>1332</v>
+        <v>1315</v>
       </c>
       <c r="D646" t="s">
         <v>1613</v>
@@ -22739,7 +22739,7 @@
         <v>961</v>
       </c>
       <c r="C649" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D649" t="s">
         <v>1616</v>
@@ -24007,13 +24007,13 @@
     </row>
     <row r="698" spans="1:8">
       <c r="A698" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B698" t="s">
         <v>959</v>
       </c>
       <c r="C698" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D698" t="s">
         <v>1614</v>
@@ -24022,7 +24022,7 @@
         <v>1636</v>
       </c>
       <c r="F698" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="G698" t="s">
         <v>1809</v>
@@ -25391,7 +25391,7 @@
         <v>1082</v>
       </c>
       <c r="C751" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D751" t="s">
         <v>1615</v>
@@ -25833,7 +25833,7 @@
         <v>1095</v>
       </c>
       <c r="C768" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D768" t="s">
         <v>1619</v>
@@ -25859,7 +25859,7 @@
         <v>959</v>
       </c>
       <c r="C769" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D769" t="s">
         <v>1616</v>
@@ -25911,7 +25911,7 @@
         <v>959</v>
       </c>
       <c r="C771" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D771" t="s">
         <v>1615</v>
@@ -25937,7 +25937,7 @@
         <v>961</v>
       </c>
       <c r="C772" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D772" t="s">
         <v>1612</v>
@@ -26015,7 +26015,7 @@
         <v>1098</v>
       </c>
       <c r="C775" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D775" t="s">
         <v>1620</v>
@@ -26041,7 +26041,7 @@
         <v>961</v>
       </c>
       <c r="C776" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D776" t="s">
         <v>1612</v>
@@ -26067,7 +26067,7 @@
         <v>1099</v>
       </c>
       <c r="C777" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D777" t="s">
         <v>1619</v>
@@ -26119,7 +26119,7 @@
         <v>1100</v>
       </c>
       <c r="C779" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D779" t="s">
         <v>1612</v>
@@ -26327,7 +26327,7 @@
         <v>1107</v>
       </c>
       <c r="C787" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D787" t="s">
         <v>1615</v>
@@ -26665,7 +26665,7 @@
         <v>1115</v>
       </c>
       <c r="C800" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D800" t="s">
         <v>1615</v>
@@ -26717,7 +26717,7 @@
         <v>1115</v>
       </c>
       <c r="C802" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D802" t="s">
         <v>1616</v>
@@ -26899,7 +26899,7 @@
         <v>1120</v>
       </c>
       <c r="C809" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D809" t="s">
         <v>1619</v>
@@ -27029,7 +27029,7 @@
         <v>961</v>
       </c>
       <c r="C814" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D814" t="s">
         <v>1612</v>
@@ -27055,7 +27055,7 @@
         <v>1124</v>
       </c>
       <c r="C815" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D815" t="s">
         <v>1621</v>
@@ -27107,7 +27107,7 @@
         <v>1125</v>
       </c>
       <c r="C817" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D817" t="s">
         <v>1620</v>
@@ -27133,7 +27133,7 @@
         <v>961</v>
       </c>
       <c r="C818" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D818" t="s">
         <v>1612</v>
@@ -27185,7 +27185,7 @@
         <v>1127</v>
       </c>
       <c r="C820" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D820" t="s">
         <v>1619</v>
@@ -27818,7 +27818,7 @@
         <v>1635</v>
       </c>
       <c r="F844" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="G844" t="s">
         <v>1816</v>
@@ -27870,7 +27870,7 @@
         <v>1635</v>
       </c>
       <c r="F846" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="G846" t="s">
         <v>1816</v>
@@ -28000,7 +28000,7 @@
         <v>1635</v>
       </c>
       <c r="F851" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="G851" t="s">
         <v>1816</v>
@@ -28667,7 +28667,7 @@
         <v>961</v>
       </c>
       <c r="C877" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D877" t="s">
         <v>1616</v>
@@ -28719,7 +28719,7 @@
         <v>1132</v>
       </c>
       <c r="C879" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D879" t="s">
         <v>1622</v>
@@ -28745,7 +28745,7 @@
         <v>1132</v>
       </c>
       <c r="C880" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D880" t="s">
         <v>1621</v>
@@ -28823,7 +28823,7 @@
         <v>958</v>
       </c>
       <c r="C883" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D883" t="s">
         <v>1612</v>
@@ -28901,7 +28901,7 @@
         <v>1135</v>
       </c>
       <c r="C886" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D886" t="s">
         <v>1619</v>
@@ -28927,7 +28927,7 @@
         <v>1136</v>
       </c>
       <c r="C887" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D887" t="s">
         <v>1620</v>
@@ -28979,7 +28979,7 @@
         <v>959</v>
       </c>
       <c r="C889" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D889" t="s">
         <v>1613</v>
@@ -29031,7 +29031,7 @@
         <v>959</v>
       </c>
       <c r="C891" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D891" t="s">
         <v>1614</v>
@@ -29109,7 +29109,7 @@
         <v>961</v>
       </c>
       <c r="C894" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D894" t="s">
         <v>1616</v>
@@ -29525,7 +29525,7 @@
         <v>1074</v>
       </c>
       <c r="C910" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D910" t="s">
         <v>1612</v>
@@ -29863,7 +29863,7 @@
         <v>959</v>
       </c>
       <c r="C923" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D923" t="s">
         <v>1616</v>
@@ -29889,7 +29889,7 @@
         <v>1145</v>
       </c>
       <c r="C924" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D924" t="s">
         <v>1613</v>
@@ -29941,7 +29941,7 @@
         <v>961</v>
       </c>
       <c r="C926" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D926" t="s">
         <v>1615</v>
@@ -29967,7 +29967,7 @@
         <v>1146</v>
       </c>
       <c r="C927" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D927" t="s">
         <v>1620</v>
@@ -30019,7 +30019,7 @@
         <v>1148</v>
       </c>
       <c r="C929" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D929" t="s">
         <v>1619</v>
@@ -30045,7 +30045,7 @@
         <v>961</v>
       </c>
       <c r="C930" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D930" t="s">
         <v>1616</v>
@@ -30253,7 +30253,7 @@
         <v>1074</v>
       </c>
       <c r="C938" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D938" t="s">
         <v>1613</v>
@@ -30279,7 +30279,7 @@
         <v>961</v>
       </c>
       <c r="C939" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D939" t="s">
         <v>1614</v>
@@ -30513,7 +30513,7 @@
         <v>959</v>
       </c>
       <c r="C948" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="D948" t="s">
         <v>1613</v>
@@ -30565,7 +30565,7 @@
         <v>959</v>
       </c>
       <c r="C950" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="D950" t="s">
         <v>1614</v>
@@ -30877,7 +30877,7 @@
         <v>959</v>
       </c>
       <c r="C962" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D962" t="s">
         <v>1616</v>
@@ -30929,7 +30929,7 @@
         <v>1155</v>
       </c>
       <c r="C964" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D964" t="s">
         <v>1622</v>
@@ -30981,7 +30981,7 @@
         <v>961</v>
       </c>
       <c r="C966" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D966" t="s">
         <v>1615</v>
@@ -31007,7 +31007,7 @@
         <v>1156</v>
       </c>
       <c r="C967" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D967" t="s">
         <v>1620</v>
@@ -31033,7 +31033,7 @@
         <v>1157</v>
       </c>
       <c r="C968" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D968" t="s">
         <v>1619</v>
@@ -31059,7 +31059,7 @@
         <v>961</v>
       </c>
       <c r="C969" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D969" t="s">
         <v>1616</v>
@@ -31657,7 +31657,7 @@
         <v>958</v>
       </c>
       <c r="C992" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D992" t="s">
         <v>1612</v>
@@ -31683,7 +31683,7 @@
         <v>959</v>
       </c>
       <c r="C993" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D993" t="s">
         <v>1613</v>
@@ -31709,7 +31709,7 @@
         <v>959</v>
       </c>
       <c r="C994" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D994" t="s">
         <v>1614</v>
@@ -31839,7 +31839,7 @@
         <v>958</v>
       </c>
       <c r="C999" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D999" t="s">
         <v>1612</v>
@@ -31865,7 +31865,7 @@
         <v>959</v>
       </c>
       <c r="C1000" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1000" t="s">
         <v>1613</v>
@@ -31917,7 +31917,7 @@
         <v>959</v>
       </c>
       <c r="C1002" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1002" t="s">
         <v>1614</v>
@@ -32853,7 +32853,7 @@
         <v>959</v>
       </c>
       <c r="C1038" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1038" t="s">
         <v>1613</v>
@@ -32879,7 +32879,7 @@
         <v>959</v>
       </c>
       <c r="C1039" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D1039" t="s">
         <v>1615</v>
@@ -32931,7 +32931,7 @@
         <v>958</v>
       </c>
       <c r="C1041" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1041" t="s">
         <v>1612</v>
@@ -32957,7 +32957,7 @@
         <v>958</v>
       </c>
       <c r="C1042" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1042" t="s">
         <v>1615</v>
@@ -33243,7 +33243,7 @@
         <v>959</v>
       </c>
       <c r="C1053" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1053" t="s">
         <v>1612</v>
@@ -33451,7 +33451,7 @@
         <v>1183</v>
       </c>
       <c r="C1061" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D1061" t="s">
         <v>1613</v>
@@ -33841,7 +33841,7 @@
         <v>1193</v>
       </c>
       <c r="C1076" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D1076" t="s">
         <v>1617</v>
@@ -33867,7 +33867,7 @@
         <v>958</v>
       </c>
       <c r="C1077" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1077" t="s">
         <v>1613</v>
@@ -33893,7 +33893,7 @@
         <v>961</v>
       </c>
       <c r="C1078" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1078" t="s">
         <v>1614</v>
@@ -33945,7 +33945,7 @@
         <v>1194</v>
       </c>
       <c r="C1080" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D1080" t="s">
         <v>1620</v>
@@ -33971,7 +33971,7 @@
         <v>958</v>
       </c>
       <c r="C1081" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1081" t="s">
         <v>1612</v>
@@ -33997,7 +33997,7 @@
         <v>958</v>
       </c>
       <c r="C1082" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1082" t="s">
         <v>1615</v>
@@ -34049,7 +34049,7 @@
         <v>959</v>
       </c>
       <c r="C1084" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D1084" t="s">
         <v>1613</v>
@@ -34205,7 +34205,7 @@
         <v>959</v>
       </c>
       <c r="C1090" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1090" t="s">
         <v>1613</v>
@@ -35375,7 +35375,7 @@
         <v>961</v>
       </c>
       <c r="C1135" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D1135" t="s">
         <v>1612</v>
@@ -35401,7 +35401,7 @@
         <v>958</v>
       </c>
       <c r="C1136" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1136" t="s">
         <v>1615</v>
@@ -35427,7 +35427,7 @@
         <v>1198</v>
       </c>
       <c r="C1137" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D1137" t="s">
         <v>1616</v>
@@ -35453,7 +35453,7 @@
         <v>958</v>
       </c>
       <c r="C1138" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1138" t="s">
         <v>1612</v>
@@ -35479,7 +35479,7 @@
         <v>958</v>
       </c>
       <c r="C1139" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1139" t="s">
         <v>1615</v>
@@ -35505,7 +35505,7 @@
         <v>1199</v>
       </c>
       <c r="C1140" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1140" t="s">
         <v>1617</v>
@@ -35531,7 +35531,7 @@
         <v>1200</v>
       </c>
       <c r="C1141" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1141" t="s">
         <v>1613</v>
@@ -35557,7 +35557,7 @@
         <v>1201</v>
       </c>
       <c r="C1142" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1142" t="s">
         <v>1614</v>
@@ -35609,7 +35609,7 @@
         <v>1203</v>
       </c>
       <c r="C1144" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D1144" t="s">
         <v>1617</v>
@@ -35635,7 +35635,7 @@
         <v>959</v>
       </c>
       <c r="C1145" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1145" t="s">
         <v>1613</v>
@@ -35661,7 +35661,7 @@
         <v>958</v>
       </c>
       <c r="C1146" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1146" t="s">
         <v>1615</v>
@@ -35687,7 +35687,7 @@
         <v>1204</v>
       </c>
       <c r="C1147" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D1147" t="s">
         <v>1620</v>
@@ -35765,7 +35765,7 @@
         <v>1205</v>
       </c>
       <c r="C1150" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1150" t="s">
         <v>1613</v>
@@ -35791,7 +35791,7 @@
         <v>1206</v>
       </c>
       <c r="C1151" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D1151" t="s">
         <v>1613</v>
@@ -35817,7 +35817,7 @@
         <v>1205</v>
       </c>
       <c r="C1152" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1152" t="s">
         <v>1614</v>
@@ -35843,7 +35843,7 @@
         <v>1206</v>
       </c>
       <c r="C1153" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D1153" t="s">
         <v>1614</v>
@@ -36077,7 +36077,7 @@
         <v>958</v>
       </c>
       <c r="C1162" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1162" t="s">
         <v>1612</v>
@@ -36103,7 +36103,7 @@
         <v>958</v>
       </c>
       <c r="C1163" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1163" t="s">
         <v>1615</v>
@@ -36155,7 +36155,7 @@
         <v>1213</v>
       </c>
       <c r="C1165" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D1165" t="s">
         <v>1622</v>
@@ -36181,7 +36181,7 @@
         <v>1214</v>
       </c>
       <c r="C1166" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D1166" t="s">
         <v>1621</v>
@@ -36233,7 +36233,7 @@
         <v>958</v>
       </c>
       <c r="C1168" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D1168" t="s">
         <v>1612</v>
@@ -36259,7 +36259,7 @@
         <v>959</v>
       </c>
       <c r="C1169" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1169" t="s">
         <v>1613</v>
@@ -36337,7 +36337,7 @@
         <v>1218</v>
       </c>
       <c r="C1172" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D1172" t="s">
         <v>1622</v>
@@ -36961,7 +36961,7 @@
         <v>1220</v>
       </c>
       <c r="C1196" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D1196" t="s">
         <v>1622</v>
@@ -36987,7 +36987,7 @@
         <v>958</v>
       </c>
       <c r="C1197" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1197" t="s">
         <v>1615</v>
@@ -36996,7 +36996,7 @@
         <v>1635</v>
       </c>
       <c r="F1197" t="s">
-        <v>1646</v>
+        <v>1652</v>
       </c>
       <c r="G1197" t="s">
         <v>1833</v>
@@ -37013,7 +37013,7 @@
         <v>1221</v>
       </c>
       <c r="C1198" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1198" t="s">
         <v>1620</v>
@@ -37022,7 +37022,7 @@
         <v>1635</v>
       </c>
       <c r="F1198" t="s">
-        <v>1646</v>
+        <v>1652</v>
       </c>
       <c r="G1198" t="s">
         <v>1833</v>
@@ -37039,7 +37039,7 @@
         <v>958</v>
       </c>
       <c r="C1199" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1199" t="s">
         <v>1612</v>
@@ -37065,7 +37065,7 @@
         <v>958</v>
       </c>
       <c r="C1200" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1200" t="s">
         <v>1615</v>
@@ -37091,7 +37091,7 @@
         <v>958</v>
       </c>
       <c r="C1201" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1201" t="s">
         <v>1613</v>
@@ -37117,7 +37117,7 @@
         <v>961</v>
       </c>
       <c r="C1202" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1202" t="s">
         <v>1614</v>
@@ -37143,7 +37143,7 @@
         <v>959</v>
       </c>
       <c r="C1203" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1203" t="s">
         <v>1615</v>
@@ -37169,7 +37169,7 @@
         <v>1222</v>
       </c>
       <c r="C1204" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1204" t="s">
         <v>1620</v>
@@ -37195,7 +37195,7 @@
         <v>961</v>
       </c>
       <c r="C1205" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1205" t="s">
         <v>1612</v>
@@ -37221,7 +37221,7 @@
         <v>961</v>
       </c>
       <c r="C1206" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D1206" t="s">
         <v>1613</v>
@@ -37247,7 +37247,7 @@
         <v>958</v>
       </c>
       <c r="C1207" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D1207" t="s">
         <v>1615</v>
@@ -37273,7 +37273,7 @@
         <v>958</v>
       </c>
       <c r="C1208" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1208" t="s">
         <v>1616</v>
@@ -37299,7 +37299,7 @@
         <v>1223</v>
       </c>
       <c r="C1209" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1209" t="s">
         <v>1617</v>
@@ -37325,7 +37325,7 @@
         <v>959</v>
       </c>
       <c r="C1210" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1210" t="s">
         <v>1613</v>
@@ -37351,7 +37351,7 @@
         <v>1224</v>
       </c>
       <c r="C1211" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D1211" t="s">
         <v>1619</v>
@@ -37377,7 +37377,7 @@
         <v>961</v>
       </c>
       <c r="C1212" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D1212" t="s">
         <v>1616</v>
@@ -37429,7 +37429,7 @@
         <v>958</v>
       </c>
       <c r="C1214" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1214" t="s">
         <v>1615</v>
@@ -37455,7 +37455,7 @@
         <v>961</v>
       </c>
       <c r="C1215" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1215" t="s">
         <v>1616</v>
@@ -41430,10 +41430,10 @@
         <v>831</v>
       </c>
       <c r="B1368" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C1368" t="s">
-        <v>1312</v>
+        <v>1388</v>
       </c>
       <c r="D1368" t="s">
         <v>1613</v>
@@ -41442,7 +41442,7 @@
         <v>1635</v>
       </c>
       <c r="F1368" t="s">
-        <v>1642</v>
+        <v>1778</v>
       </c>
       <c r="G1368" t="s">
         <v>1837</v>
@@ -41456,10 +41456,10 @@
         <v>832</v>
       </c>
       <c r="B1369" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="C1369" t="s">
-        <v>1388</v>
+        <v>1312</v>
       </c>
       <c r="D1369" t="s">
         <v>1613</v>
@@ -41468,7 +41468,7 @@
         <v>1635</v>
       </c>
       <c r="F1369" t="s">
-        <v>1778</v>
+        <v>1642</v>
       </c>
       <c r="G1369" t="s">
         <v>1837</v>
@@ -41531,13 +41531,13 @@
     </row>
     <row r="1372" spans="1:8">
       <c r="A1372" t="s">
-        <v>833</v>
+        <v>361</v>
       </c>
       <c r="B1372" t="s">
-        <v>1226</v>
+        <v>961</v>
       </c>
       <c r="C1372" t="s">
-        <v>1312</v>
+        <v>1566</v>
       </c>
       <c r="D1372" t="s">
         <v>1614</v>
@@ -41546,7 +41546,7 @@
         <v>1635</v>
       </c>
       <c r="F1372" t="s">
-        <v>1642</v>
+        <v>1681</v>
       </c>
       <c r="G1372" t="s">
         <v>1837</v>
@@ -41557,13 +41557,13 @@
     </row>
     <row r="1373" spans="1:8">
       <c r="A1373" t="s">
-        <v>361</v>
+        <v>833</v>
       </c>
       <c r="B1373" t="s">
-        <v>961</v>
+        <v>1226</v>
       </c>
       <c r="C1373" t="s">
-        <v>1566</v>
+        <v>1312</v>
       </c>
       <c r="D1373" t="s">
         <v>1614</v>
@@ -41572,7 +41572,7 @@
         <v>1635</v>
       </c>
       <c r="F1373" t="s">
-        <v>1681</v>
+        <v>1642</v>
       </c>
       <c r="G1373" t="s">
         <v>1837</v>
@@ -42135,7 +42135,7 @@
         <v>958</v>
       </c>
       <c r="C1395" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1395" t="s">
         <v>1612</v>
@@ -42499,7 +42499,7 @@
         <v>958</v>
       </c>
       <c r="C1409" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1409" t="s">
         <v>1615</v>
@@ -42603,7 +42603,7 @@
         <v>1225</v>
       </c>
       <c r="C1413" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D1413" t="s">
         <v>1612</v>
@@ -42811,7 +42811,7 @@
         <v>1230</v>
       </c>
       <c r="C1421" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1421" t="s">
         <v>1613</v>
@@ -42915,7 +42915,7 @@
         <v>1230</v>
       </c>
       <c r="C1425" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1425" t="s">
         <v>1614</v>
@@ -43253,7 +43253,7 @@
         <v>1225</v>
       </c>
       <c r="C1438" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D1438" t="s">
         <v>1615</v>
@@ -43990,7 +43990,7 @@
         <v>1636</v>
       </c>
       <c r="F1466" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="G1466" t="s">
         <v>1838</v>
@@ -44160,7 +44160,7 @@
         <v>891</v>
       </c>
       <c r="B1473" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="C1473" t="s">
         <v>1589</v>
@@ -44186,7 +44186,7 @@
         <v>892</v>
       </c>
       <c r="B1474" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C1474" t="s">
         <v>1590</v>
@@ -44198,7 +44198,7 @@
         <v>1637</v>
       </c>
       <c r="F1474" t="s">
-        <v>1787</v>
+        <v>1783</v>
       </c>
       <c r="G1474" t="s">
         <v>1838</v>
@@ -44250,7 +44250,7 @@
         <v>1637</v>
       </c>
       <c r="F1476" t="s">
-        <v>1783</v>
+        <v>1787</v>
       </c>
       <c r="G1476" t="s">
         <v>1838</v>
@@ -44874,7 +44874,7 @@
         <v>1638</v>
       </c>
       <c r="F1500" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="G1500" t="s">
         <v>1838</v>
@@ -44969,7 +44969,7 @@
         <v>961</v>
       </c>
       <c r="C1504" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1504" t="s">
         <v>1612</v>
@@ -45151,7 +45151,7 @@
         <v>961</v>
       </c>
       <c r="C1511" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1511" t="s">
         <v>1616</v>
@@ -45229,7 +45229,7 @@
         <v>959</v>
       </c>
       <c r="C1514" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1514" t="s">
         <v>1612</v>
@@ -45255,7 +45255,7 @@
         <v>959</v>
       </c>
       <c r="C1515" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1515" t="s">
         <v>1612</v>
@@ -45281,7 +45281,7 @@
         <v>959</v>
       </c>
       <c r="C1516" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1516" t="s">
         <v>1618</v>
@@ -45307,7 +45307,7 @@
         <v>959</v>
       </c>
       <c r="C1517" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1517" t="s">
         <v>1613</v>
@@ -45359,7 +45359,7 @@
         <v>959</v>
       </c>
       <c r="C1519" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1519" t="s">
         <v>1616</v>
@@ -45385,7 +45385,7 @@
         <v>961</v>
       </c>
       <c r="C1520" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1520" t="s">
         <v>1612</v>
@@ -45515,7 +45515,7 @@
         <v>958</v>
       </c>
       <c r="C1525" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D1525" t="s">
         <v>1613</v>
@@ -45645,7 +45645,7 @@
         <v>959</v>
       </c>
       <c r="C1530" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1530" t="s">
         <v>1618</v>
@@ -45775,7 +45775,7 @@
         <v>958</v>
       </c>
       <c r="C1535" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1535" t="s">
         <v>1615</v>
@@ -45905,7 +45905,7 @@
         <v>959</v>
       </c>
       <c r="C1540" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1540" t="s">
         <v>1618</v>
@@ -45957,7 +45957,7 @@
         <v>959</v>
       </c>
       <c r="C1542" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1542" t="s">
         <v>1613</v>
@@ -46087,7 +46087,7 @@
         <v>959</v>
       </c>
       <c r="C1547" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1547" t="s">
         <v>1614</v>
@@ -46243,7 +46243,7 @@
         <v>959</v>
       </c>
       <c r="C1553" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1553" t="s">
         <v>1616</v>
@@ -47361,7 +47361,7 @@
         <v>959</v>
       </c>
       <c r="C1596" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1596" t="s">
         <v>1634</v>

--- a/EDT_Edition.xlsx
+++ b/EDT_Edition.xlsx
@@ -481,12 +481,12 @@
     <t>TD-Anglais technique</t>
   </si>
   <si>
+    <t>TP- Méthodes numériques appliquées- Python</t>
+  </si>
+  <si>
     <t>TP-Electronique appliquée</t>
   </si>
   <si>
-    <t>TP- Méthodes numériques appliquées- Python</t>
-  </si>
-  <si>
     <t>TD-Transfert thermique</t>
   </si>
   <si>
@@ -3961,208 +3961,208 @@
     <t>SEMMAK ABDELKADER</t>
   </si>
   <si>
+    <t>Non défini-ELT</t>
+  </si>
+  <si>
+    <t>KHIAT WALID</t>
+  </si>
+  <si>
+    <t>FELLAH MOHAMMED KARIM</t>
+  </si>
+  <si>
+    <t>BELAIDI OUAFIA</t>
+  </si>
+  <si>
+    <t>GRABA ABDELMADJID GUESSOUM</t>
+  </si>
+  <si>
+    <t>MOSTEFAOUI</t>
+  </si>
+  <si>
+    <t>ADDAD MOUAD</t>
+  </si>
+  <si>
+    <t>SEKKAL SIDI MOHAMMED</t>
+  </si>
+  <si>
+    <t>SEDDIKI ALI</t>
+  </si>
+  <si>
+    <t>FARAH MEHDI CHEMSEDDINE</t>
+  </si>
+  <si>
+    <t>DJEBBARI ALI</t>
+  </si>
+  <si>
+    <t>MAHIDDINE ABDERRAHIM</t>
+  </si>
+  <si>
+    <t>ABOURA LAMIA TOURIA</t>
+  </si>
+  <si>
+    <t>MESKINE FATIHA</t>
+  </si>
+  <si>
+    <t>BENHAMIDA FARID</t>
+  </si>
+  <si>
+    <t>JBILOU MOKHTARIA</t>
+  </si>
+  <si>
+    <t>GHAZEL FATIHA</t>
+  </si>
+  <si>
+    <t>BENDIMERAD SALAH EDDINE</t>
+  </si>
+  <si>
+    <t>MEGUEDAD ABOUBAKR</t>
+  </si>
+  <si>
+    <t>BECHEKIR SEYF EDDINE</t>
+  </si>
+  <si>
+    <t>DJELLOULI YOUNES</t>
+  </si>
+  <si>
+    <t>TOUHAMI SEDDIK</t>
+  </si>
+  <si>
+    <t>NASSOUR KAMEL</t>
+  </si>
+  <si>
+    <t>AYAD ABDELGHANI</t>
+  </si>
+  <si>
+    <t>SEMMAH ABDELHAFID</t>
+  </si>
+  <si>
+    <t>BOUBEKEUR HALIMA</t>
+  </si>
+  <si>
+    <t>MANSOURI ABDERRAZAK</t>
+  </si>
+  <si>
+    <t>ZIDI SID AHMED</t>
+  </si>
+  <si>
+    <t>HADJ BOULANOUAR RACHID</t>
+  </si>
+  <si>
+    <t>REGUIEG ZAKARIA</t>
+  </si>
+  <si>
+    <t>BOUKHOULDA FODIL</t>
+  </si>
+  <si>
+    <t>NEMMICH SAID</t>
+  </si>
+  <si>
+    <t>MEKHFI KHALIDA</t>
+  </si>
+  <si>
+    <t>REZOUG MOHAMMED</t>
+  </si>
+  <si>
+    <t>MILOUA FARID</t>
+  </si>
+  <si>
+    <t>BELLEBNA YASSINE</t>
+  </si>
+  <si>
+    <t>MAAMMAR MOHAMED</t>
+  </si>
+  <si>
+    <t>BAHLIL MOUNIR</t>
+  </si>
+  <si>
+    <t>MECHETTEM KHALIDA</t>
+  </si>
+  <si>
+    <t>BENSEDDIK NADIA</t>
+  </si>
+  <si>
+    <t>CHIRANI SOUMIA</t>
+  </si>
+  <si>
+    <t>LARBI ZIDI</t>
+  </si>
+  <si>
+    <t>DOUIAICI MOHAMED</t>
+  </si>
+  <si>
+    <t>BEDDAD BOUCIF</t>
+  </si>
+  <si>
+    <t>BELHALLOUCHE LAKHDAR</t>
+  </si>
+  <si>
+    <t>ATTAR IMAD</t>
+  </si>
+  <si>
+    <t>BENSALEM MOHAMMED MUSTAPHA</t>
+  </si>
+  <si>
+    <t>DRIEF FAIZA</t>
+  </si>
+  <si>
+    <t>BENOUAR MOHAMED</t>
+  </si>
+  <si>
+    <t>ELGHODASSE ABDEL MADJID</t>
+  </si>
+  <si>
+    <t>HAMMAR MEHDI</t>
+  </si>
+  <si>
+    <t>IKKACHE NARIMEN</t>
+  </si>
+  <si>
+    <t>SAHRAOUI HADIL</t>
+  </si>
+  <si>
+    <t>MELIANI ABDELHAK</t>
+  </si>
+  <si>
+    <t>KADRI RANIA</t>
+  </si>
+  <si>
+    <t>BOULARAF AICHA</t>
+  </si>
+  <si>
+    <t>TALEB SOUMIA</t>
+  </si>
+  <si>
+    <t>BENMESSAOUD LEYLA</t>
+  </si>
+  <si>
+    <t>SAYAH RAFIK</t>
+  </si>
+  <si>
+    <t>NON DÉFINI-AUTO</t>
+  </si>
+  <si>
+    <t>BENSAID DJILALI</t>
+  </si>
+  <si>
+    <t>BENKHALLOUK KADDOUR</t>
+  </si>
+  <si>
+    <t>MILOUDI + BOUDRAA</t>
+  </si>
+  <si>
+    <t>BENAMARA ZINEB</t>
+  </si>
+  <si>
+    <t>BENSAID DJILALI + MASSIM</t>
+  </si>
+  <si>
+    <t>MILOUDI MOHAMED</t>
+  </si>
+  <si>
+    <t>DJEHAF MOHAMMED ABDELJALIL</t>
+  </si>
+  <si>
     <t>EL-FIAD MOHAMED DJILLALI</t>
-  </si>
-  <si>
-    <t>KHIAT WALID</t>
-  </si>
-  <si>
-    <t>FELLAH MOHAMMED KARIM</t>
-  </si>
-  <si>
-    <t>BELAIDI OUAFIA</t>
-  </si>
-  <si>
-    <t>GRABA ABDELMADJID GUESSOUM</t>
-  </si>
-  <si>
-    <t>MOSTEFAOUI</t>
-  </si>
-  <si>
-    <t>ADDAD MOUAD</t>
-  </si>
-  <si>
-    <t>SEKKAL SIDI MOHAMMED</t>
-  </si>
-  <si>
-    <t>SEDDIKI ALI</t>
-  </si>
-  <si>
-    <t>FARAH MEHDI CHEMSEDDINE</t>
-  </si>
-  <si>
-    <t>DJEBBARI ALI</t>
-  </si>
-  <si>
-    <t>MAHIDDINE ABDERRAHIM</t>
-  </si>
-  <si>
-    <t>ABOURA LAMIA TOURIA</t>
-  </si>
-  <si>
-    <t>MESKINE FATIHA</t>
-  </si>
-  <si>
-    <t>BENHAMIDA FARID</t>
-  </si>
-  <si>
-    <t>JBILOU MOKHTARIA</t>
-  </si>
-  <si>
-    <t>GHAZEL FATIHA</t>
-  </si>
-  <si>
-    <t>Non défini-ELT</t>
-  </si>
-  <si>
-    <t>BENDIMERAD SALAH EDDINE</t>
-  </si>
-  <si>
-    <t>MEGUEDAD ABOUBAKR</t>
-  </si>
-  <si>
-    <t>BECHEKIR SEYF EDDINE</t>
-  </si>
-  <si>
-    <t>DJELLOULI YOUNES</t>
-  </si>
-  <si>
-    <t>TOUHAMI SEDDIK</t>
-  </si>
-  <si>
-    <t>NASSOUR KAMEL</t>
-  </si>
-  <si>
-    <t>AYAD ABDELGHANI</t>
-  </si>
-  <si>
-    <t>SEMMAH ABDELHAFID</t>
-  </si>
-  <si>
-    <t>BOUBEKEUR HALIMA</t>
-  </si>
-  <si>
-    <t>MANSOURI ABDERRAZAK</t>
-  </si>
-  <si>
-    <t>ZIDI SID AHMED</t>
-  </si>
-  <si>
-    <t>HADJ BOULANOUAR RACHID</t>
-  </si>
-  <si>
-    <t>REGUIEG ZAKARIA</t>
-  </si>
-  <si>
-    <t>BOUKHOULDA FODIL</t>
-  </si>
-  <si>
-    <t>NEMMICH SAID</t>
-  </si>
-  <si>
-    <t>MEKHFI KHALIDA</t>
-  </si>
-  <si>
-    <t>REZOUG MOHAMMED</t>
-  </si>
-  <si>
-    <t>MILOUA FARID</t>
-  </si>
-  <si>
-    <t>BELLEBNA YASSINE</t>
-  </si>
-  <si>
-    <t>MAAMMAR MOHAMED</t>
-  </si>
-  <si>
-    <t>BAHLIL MOUNIR</t>
-  </si>
-  <si>
-    <t>MECHETTEM KHALIDA</t>
-  </si>
-  <si>
-    <t>BENSEDDIK NADIA</t>
-  </si>
-  <si>
-    <t>CHIRANI SOUMIA</t>
-  </si>
-  <si>
-    <t>LARBI ZIDI</t>
-  </si>
-  <si>
-    <t>DOUIAICI MOHAMED</t>
-  </si>
-  <si>
-    <t>BEDDAD BOUCIF</t>
-  </si>
-  <si>
-    <t>BELHALLOUCHE LAKHDAR</t>
-  </si>
-  <si>
-    <t>ATTAR IMAD</t>
-  </si>
-  <si>
-    <t>BENSALEM MOHAMMED MUSTAPHA</t>
-  </si>
-  <si>
-    <t>DRIEF FAIZA</t>
-  </si>
-  <si>
-    <t>BENOUAR MOHAMED</t>
-  </si>
-  <si>
-    <t>ELGHODASSE ABDEL MADJID</t>
-  </si>
-  <si>
-    <t>HAMMAR MEHDI</t>
-  </si>
-  <si>
-    <t>IKKACHE NARIMEN</t>
-  </si>
-  <si>
-    <t>SAHRAOUI HADIL</t>
-  </si>
-  <si>
-    <t>MELIANI ABDELHAK</t>
-  </si>
-  <si>
-    <t>KADRI RANIA</t>
-  </si>
-  <si>
-    <t>BOULARAF AICHA</t>
-  </si>
-  <si>
-    <t>TALEB SOUMIA</t>
-  </si>
-  <si>
-    <t>BENMESSAOUD LEYLA</t>
-  </si>
-  <si>
-    <t>SAYAH RAFIK</t>
-  </si>
-  <si>
-    <t>NON DÉFINI-AUTO</t>
-  </si>
-  <si>
-    <t>BENSAID DJILALI</t>
-  </si>
-  <si>
-    <t>BENKHALLOUK KADDOUR</t>
-  </si>
-  <si>
-    <t>MILOUDI + BOUDRAA</t>
-  </si>
-  <si>
-    <t>BENAMARA ZINEB</t>
-  </si>
-  <si>
-    <t>BENSAID DJILALI + MASSIM</t>
-  </si>
-  <si>
-    <t>MILOUDI MOHAMED</t>
-  </si>
-  <si>
-    <t>DJEHAF MOHAMMED ABDELJALIL</t>
   </si>
   <si>
     <t>MEDLES IMED</t>
@@ -11715,7 +11715,7 @@
         <v>959</v>
       </c>
       <c r="C225" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="D225" t="s">
         <v>1613</v>
@@ -11724,7 +11724,7 @@
         <v>1639</v>
       </c>
       <c r="F225" t="s">
-        <v>1690</v>
+        <v>1642</v>
       </c>
       <c r="G225" t="s">
         <v>1795</v>
@@ -11741,7 +11741,7 @@
         <v>959</v>
       </c>
       <c r="C226" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="D226" t="s">
         <v>1613</v>
@@ -11750,7 +11750,7 @@
         <v>1639</v>
       </c>
       <c r="F226" t="s">
-        <v>1642</v>
+        <v>1690</v>
       </c>
       <c r="G226" t="s">
         <v>1795</v>
@@ -11767,7 +11767,7 @@
         <v>959</v>
       </c>
       <c r="C227" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="D227" t="s">
         <v>1614</v>
@@ -11776,7 +11776,7 @@
         <v>1639</v>
       </c>
       <c r="F227" t="s">
-        <v>1690</v>
+        <v>1642</v>
       </c>
       <c r="G227" t="s">
         <v>1795</v>
@@ -11793,7 +11793,7 @@
         <v>959</v>
       </c>
       <c r="C228" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="D228" t="s">
         <v>1614</v>
@@ -11802,7 +11802,7 @@
         <v>1639</v>
       </c>
       <c r="F228" t="s">
-        <v>1642</v>
+        <v>1690</v>
       </c>
       <c r="G228" t="s">
         <v>1795</v>
@@ -12937,7 +12937,7 @@
         <v>959</v>
       </c>
       <c r="C272" t="s">
-        <v>1332</v>
+        <v>1315</v>
       </c>
       <c r="D272" t="s">
         <v>1612</v>
@@ -12989,7 +12989,7 @@
         <v>959</v>
       </c>
       <c r="C274" t="s">
-        <v>1332</v>
+        <v>1315</v>
       </c>
       <c r="D274" t="s">
         <v>1616</v>
@@ -13015,7 +13015,7 @@
         <v>958</v>
       </c>
       <c r="C275" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D275" t="s">
         <v>1612</v>
@@ -13067,7 +13067,7 @@
         <v>978</v>
       </c>
       <c r="C277" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D277" t="s">
         <v>1622</v>
@@ -13119,7 +13119,7 @@
         <v>961</v>
       </c>
       <c r="C279" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="D279" t="s">
         <v>1615</v>
@@ -13145,7 +13145,7 @@
         <v>961</v>
       </c>
       <c r="C280" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="D280" t="s">
         <v>1616</v>
@@ -13249,7 +13249,7 @@
         <v>959</v>
       </c>
       <c r="C284" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D284" t="s">
         <v>1612</v>
@@ -13275,7 +13275,7 @@
         <v>959</v>
       </c>
       <c r="C285" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D285" t="s">
         <v>1612</v>
@@ -13301,7 +13301,7 @@
         <v>959</v>
       </c>
       <c r="C286" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="D286" t="s">
         <v>1613</v>
@@ -13353,7 +13353,7 @@
         <v>959</v>
       </c>
       <c r="C288" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="D288" t="s">
         <v>1614</v>
@@ -13405,7 +13405,7 @@
         <v>958</v>
       </c>
       <c r="C290" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D290" t="s">
         <v>1615</v>
@@ -13431,7 +13431,7 @@
         <v>959</v>
       </c>
       <c r="C291" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D291" t="s">
         <v>1616</v>
@@ -13457,7 +13457,7 @@
         <v>959</v>
       </c>
       <c r="C292" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D292" t="s">
         <v>1616</v>
@@ -13561,7 +13561,7 @@
         <v>958</v>
       </c>
       <c r="C296" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D296" t="s">
         <v>1615</v>
@@ -13613,7 +13613,7 @@
         <v>982</v>
       </c>
       <c r="C298" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D298" t="s">
         <v>1619</v>
@@ -13639,7 +13639,7 @@
         <v>983</v>
       </c>
       <c r="C299" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D299" t="s">
         <v>1619</v>
@@ -13665,7 +13665,7 @@
         <v>982</v>
       </c>
       <c r="C300" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D300" t="s">
         <v>1620</v>
@@ -13691,7 +13691,7 @@
         <v>983</v>
       </c>
       <c r="C301" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D301" t="s">
         <v>1620</v>
@@ -13717,7 +13717,7 @@
         <v>984</v>
       </c>
       <c r="C302" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D302" t="s">
         <v>1617</v>
@@ -13795,7 +13795,7 @@
         <v>985</v>
       </c>
       <c r="C305" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D305" t="s">
         <v>1619</v>
@@ -13821,7 +13821,7 @@
         <v>958</v>
       </c>
       <c r="C306" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D306" t="s">
         <v>1616</v>
@@ -13847,7 +13847,7 @@
         <v>961</v>
       </c>
       <c r="C307" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D307" t="s">
         <v>1612</v>
@@ -13873,7 +13873,7 @@
         <v>958</v>
       </c>
       <c r="C308" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="D308" t="s">
         <v>1615</v>
@@ -13899,7 +13899,7 @@
         <v>986</v>
       </c>
       <c r="C309" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D309" t="s">
         <v>1620</v>
@@ -13925,7 +13925,7 @@
         <v>959</v>
       </c>
       <c r="C310" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D310" t="s">
         <v>1612</v>
@@ -13951,7 +13951,7 @@
         <v>959</v>
       </c>
       <c r="C311" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D311" t="s">
         <v>1618</v>
@@ -13977,7 +13977,7 @@
         <v>959</v>
       </c>
       <c r="C312" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D312" t="s">
         <v>1613</v>
@@ -14003,7 +14003,7 @@
         <v>959</v>
       </c>
       <c r="C313" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D313" t="s">
         <v>1614</v>
@@ -14029,7 +14029,7 @@
         <v>987</v>
       </c>
       <c r="C314" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D314" t="s">
         <v>1619</v>
@@ -14055,7 +14055,7 @@
         <v>961</v>
       </c>
       <c r="C315" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D315" t="s">
         <v>1616</v>
@@ -14081,7 +14081,7 @@
         <v>959</v>
       </c>
       <c r="C316" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D316" t="s">
         <v>1612</v>
@@ -14159,7 +14159,7 @@
         <v>961</v>
       </c>
       <c r="C319" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D319" t="s">
         <v>1615</v>
@@ -14185,7 +14185,7 @@
         <v>958</v>
       </c>
       <c r="C320" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D320" t="s">
         <v>1616</v>
@@ -14211,7 +14211,7 @@
         <v>958</v>
       </c>
       <c r="C321" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D321" t="s">
         <v>1616</v>
@@ -14237,7 +14237,7 @@
         <v>961</v>
       </c>
       <c r="C322" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D322" t="s">
         <v>1612</v>
@@ -14263,7 +14263,7 @@
         <v>958</v>
       </c>
       <c r="C323" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D323" t="s">
         <v>1613</v>
@@ -14289,7 +14289,7 @@
         <v>961</v>
       </c>
       <c r="C324" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D324" t="s">
         <v>1614</v>
@@ -14315,7 +14315,7 @@
         <v>959</v>
       </c>
       <c r="C325" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D325" t="s">
         <v>1615</v>
@@ -14341,7 +14341,7 @@
         <v>958</v>
       </c>
       <c r="C326" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D326" t="s">
         <v>1616</v>
@@ -14367,7 +14367,7 @@
         <v>961</v>
       </c>
       <c r="C327" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D327" t="s">
         <v>1612</v>
@@ -14393,7 +14393,7 @@
         <v>959</v>
       </c>
       <c r="C328" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D328" t="s">
         <v>1613</v>
@@ -14419,7 +14419,7 @@
         <v>958</v>
       </c>
       <c r="C329" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D329" t="s">
         <v>1614</v>
@@ -14445,7 +14445,7 @@
         <v>958</v>
       </c>
       <c r="C330" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D330" t="s">
         <v>1615</v>
@@ -14471,7 +14471,7 @@
         <v>958</v>
       </c>
       <c r="C331" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D331" t="s">
         <v>1616</v>
@@ -14497,7 +14497,7 @@
         <v>958</v>
       </c>
       <c r="C332" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D332" t="s">
         <v>1612</v>
@@ -14523,7 +14523,7 @@
         <v>959</v>
       </c>
       <c r="C333" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D333" t="s">
         <v>1613</v>
@@ -14601,7 +14601,7 @@
         <v>988</v>
       </c>
       <c r="C336" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D336" t="s">
         <v>1612</v>
@@ -14627,7 +14627,7 @@
         <v>989</v>
       </c>
       <c r="C337" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D337" t="s">
         <v>1612</v>
@@ -14653,7 +14653,7 @@
         <v>959</v>
       </c>
       <c r="C338" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D338" t="s">
         <v>1612</v>
@@ -14731,7 +14731,7 @@
         <v>988</v>
       </c>
       <c r="C341" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D341" t="s">
         <v>1618</v>
@@ -14757,7 +14757,7 @@
         <v>989</v>
       </c>
       <c r="C342" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D342" t="s">
         <v>1618</v>
@@ -14783,7 +14783,7 @@
         <v>959</v>
       </c>
       <c r="C343" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D343" t="s">
         <v>1618</v>
@@ -14861,7 +14861,7 @@
         <v>988</v>
       </c>
       <c r="C346" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D346" t="s">
         <v>1613</v>
@@ -14887,7 +14887,7 @@
         <v>959</v>
       </c>
       <c r="C347" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D347" t="s">
         <v>1613</v>
@@ -14913,7 +14913,7 @@
         <v>989</v>
       </c>
       <c r="C348" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D348" t="s">
         <v>1613</v>
@@ -14939,7 +14939,7 @@
         <v>959</v>
       </c>
       <c r="C349" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D349" t="s">
         <v>1613</v>
@@ -14965,7 +14965,7 @@
         <v>988</v>
       </c>
       <c r="C350" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D350" t="s">
         <v>1614</v>
@@ -14991,7 +14991,7 @@
         <v>959</v>
       </c>
       <c r="C351" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D351" t="s">
         <v>1614</v>
@@ -15017,7 +15017,7 @@
         <v>989</v>
       </c>
       <c r="C352" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D352" t="s">
         <v>1614</v>
@@ -15043,7 +15043,7 @@
         <v>959</v>
       </c>
       <c r="C353" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D353" t="s">
         <v>1614</v>
@@ -15069,7 +15069,7 @@
         <v>958</v>
       </c>
       <c r="C354" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D354" t="s">
         <v>1615</v>
@@ -15121,7 +15121,7 @@
         <v>990</v>
       </c>
       <c r="C356" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D356" t="s">
         <v>1616</v>
@@ -15173,7 +15173,7 @@
         <v>991</v>
       </c>
       <c r="C358" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D358" t="s">
         <v>1612</v>
@@ -15199,7 +15199,7 @@
         <v>991</v>
       </c>
       <c r="C359" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D359" t="s">
         <v>1618</v>
@@ -15225,7 +15225,7 @@
         <v>959</v>
       </c>
       <c r="C360" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D360" t="s">
         <v>1613</v>
@@ -15251,7 +15251,7 @@
         <v>959</v>
       </c>
       <c r="C361" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D361" t="s">
         <v>1613</v>
@@ -15277,7 +15277,7 @@
         <v>991</v>
       </c>
       <c r="C362" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D362" t="s">
         <v>1613</v>
@@ -15303,7 +15303,7 @@
         <v>959</v>
       </c>
       <c r="C363" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D363" t="s">
         <v>1614</v>
@@ -15329,7 +15329,7 @@
         <v>959</v>
       </c>
       <c r="C364" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D364" t="s">
         <v>1614</v>
@@ -15355,7 +15355,7 @@
         <v>991</v>
       </c>
       <c r="C365" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D365" t="s">
         <v>1614</v>
@@ -15433,7 +15433,7 @@
         <v>959</v>
       </c>
       <c r="C368" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D368" t="s">
         <v>1623</v>
@@ -15459,7 +15459,7 @@
         <v>959</v>
       </c>
       <c r="C369" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D369" t="s">
         <v>1623</v>
@@ -15485,7 +15485,7 @@
         <v>959</v>
       </c>
       <c r="C370" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D370" t="s">
         <v>1624</v>
@@ -15511,7 +15511,7 @@
         <v>961</v>
       </c>
       <c r="C371" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D371" t="s">
         <v>1612</v>
@@ -15537,7 +15537,7 @@
         <v>961</v>
       </c>
       <c r="C372" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D372" t="s">
         <v>1612</v>
@@ -15563,7 +15563,7 @@
         <v>961</v>
       </c>
       <c r="C373" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D373" t="s">
         <v>1612</v>
@@ -15589,7 +15589,7 @@
         <v>959</v>
       </c>
       <c r="C374" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D374" t="s">
         <v>1625</v>
@@ -15615,7 +15615,7 @@
         <v>959</v>
       </c>
       <c r="C375" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D375" t="s">
         <v>1625</v>
@@ -15641,7 +15641,7 @@
         <v>961</v>
       </c>
       <c r="C376" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D376" t="s">
         <v>1618</v>
@@ -15667,7 +15667,7 @@
         <v>961</v>
       </c>
       <c r="C377" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D377" t="s">
         <v>1618</v>
@@ -15693,7 +15693,7 @@
         <v>959</v>
       </c>
       <c r="C378" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D378" t="s">
         <v>1626</v>
@@ -15719,7 +15719,7 @@
         <v>959</v>
       </c>
       <c r="C379" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D379" t="s">
         <v>1626</v>
@@ -15745,7 +15745,7 @@
         <v>961</v>
       </c>
       <c r="C380" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D380" t="s">
         <v>1613</v>
@@ -15771,7 +15771,7 @@
         <v>961</v>
       </c>
       <c r="C381" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D381" t="s">
         <v>1613</v>
@@ -15797,7 +15797,7 @@
         <v>961</v>
       </c>
       <c r="C382" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="D382" t="s">
         <v>1613</v>
@@ -15823,7 +15823,7 @@
         <v>959</v>
       </c>
       <c r="C383" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D383" t="s">
         <v>1613</v>
@@ -15849,7 +15849,7 @@
         <v>961</v>
       </c>
       <c r="C384" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D384" t="s">
         <v>1613</v>
@@ -15875,7 +15875,7 @@
         <v>992</v>
       </c>
       <c r="C385" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D385" t="s">
         <v>1613</v>
@@ -15901,7 +15901,7 @@
         <v>988</v>
       </c>
       <c r="C386" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D386" t="s">
         <v>1614</v>
@@ -15927,7 +15927,7 @@
         <v>961</v>
       </c>
       <c r="C387" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D387" t="s">
         <v>1614</v>
@@ -15953,7 +15953,7 @@
         <v>961</v>
       </c>
       <c r="C388" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="D388" t="s">
         <v>1614</v>
@@ -15979,7 +15979,7 @@
         <v>959</v>
       </c>
       <c r="C389" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D389" t="s">
         <v>1614</v>
@@ -16005,7 +16005,7 @@
         <v>992</v>
       </c>
       <c r="C390" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D390" t="s">
         <v>1614</v>
@@ -16031,7 +16031,7 @@
         <v>959</v>
       </c>
       <c r="C391" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D391" t="s">
         <v>1627</v>
@@ -16057,7 +16057,7 @@
         <v>959</v>
       </c>
       <c r="C392" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="D392" t="s">
         <v>1627</v>
@@ -16083,7 +16083,7 @@
         <v>961</v>
       </c>
       <c r="C393" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D393" t="s">
         <v>1615</v>
@@ -16109,7 +16109,7 @@
         <v>959</v>
       </c>
       <c r="C394" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D394" t="s">
         <v>1615</v>
@@ -16135,7 +16135,7 @@
         <v>959</v>
       </c>
       <c r="C395" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D395" t="s">
         <v>1628</v>
@@ -16161,7 +16161,7 @@
         <v>959</v>
       </c>
       <c r="C396" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D396" t="s">
         <v>1628</v>
@@ -16187,7 +16187,7 @@
         <v>959</v>
       </c>
       <c r="C397" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="D397" t="s">
         <v>1628</v>
@@ -16213,7 +16213,7 @@
         <v>991</v>
       </c>
       <c r="C398" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D398" t="s">
         <v>1616</v>
@@ -16239,7 +16239,7 @@
         <v>959</v>
       </c>
       <c r="C399" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D399" t="s">
         <v>1616</v>
@@ -16291,7 +16291,7 @@
         <v>959</v>
       </c>
       <c r="C401" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D401" t="s">
         <v>1624</v>
@@ -16317,7 +16317,7 @@
         <v>988</v>
       </c>
       <c r="C402" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D402" t="s">
         <v>1612</v>
@@ -16343,7 +16343,7 @@
         <v>991</v>
       </c>
       <c r="C403" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D403" t="s">
         <v>1612</v>
@@ -16421,7 +16421,7 @@
         <v>959</v>
       </c>
       <c r="C406" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D406" t="s">
         <v>1625</v>
@@ -16447,7 +16447,7 @@
         <v>961</v>
       </c>
       <c r="C407" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D407" t="s">
         <v>1618</v>
@@ -16473,7 +16473,7 @@
         <v>988</v>
       </c>
       <c r="C408" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D408" t="s">
         <v>1618</v>
@@ -16499,7 +16499,7 @@
         <v>991</v>
       </c>
       <c r="C409" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D409" t="s">
         <v>1618</v>
@@ -16525,7 +16525,7 @@
         <v>961</v>
       </c>
       <c r="C410" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D410" t="s">
         <v>1618</v>
@@ -16551,7 +16551,7 @@
         <v>988</v>
       </c>
       <c r="C411" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D411" t="s">
         <v>1613</v>
@@ -16577,7 +16577,7 @@
         <v>959</v>
       </c>
       <c r="C412" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D412" t="s">
         <v>1613</v>
@@ -16603,7 +16603,7 @@
         <v>991</v>
       </c>
       <c r="C413" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D413" t="s">
         <v>1613</v>
@@ -16655,7 +16655,7 @@
         <v>992</v>
       </c>
       <c r="C415" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D415" t="s">
         <v>1613</v>
@@ -16707,7 +16707,7 @@
         <v>988</v>
       </c>
       <c r="C417" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D417" t="s">
         <v>1614</v>
@@ -16733,7 +16733,7 @@
         <v>959</v>
       </c>
       <c r="C418" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D418" t="s">
         <v>1614</v>
@@ -16759,7 +16759,7 @@
         <v>991</v>
       </c>
       <c r="C419" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D419" t="s">
         <v>1614</v>
@@ -16785,7 +16785,7 @@
         <v>961</v>
       </c>
       <c r="C420" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D420" t="s">
         <v>1614</v>
@@ -16811,7 +16811,7 @@
         <v>992</v>
       </c>
       <c r="C421" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D421" t="s">
         <v>1614</v>
@@ -16863,7 +16863,7 @@
         <v>958</v>
       </c>
       <c r="C423" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D423" t="s">
         <v>1615</v>
@@ -16889,7 +16889,7 @@
         <v>958</v>
       </c>
       <c r="C424" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D424" t="s">
         <v>1615</v>
@@ -16915,7 +16915,7 @@
         <v>990</v>
       </c>
       <c r="C425" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D425" t="s">
         <v>1616</v>
@@ -16941,7 +16941,7 @@
         <v>993</v>
       </c>
       <c r="C426" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D426" t="s">
         <v>1616</v>
@@ -16993,7 +16993,7 @@
         <v>961</v>
       </c>
       <c r="C428" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D428" t="s">
         <v>1612</v>
@@ -17019,7 +17019,7 @@
         <v>959</v>
       </c>
       <c r="C429" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D429" t="s">
         <v>1612</v>
@@ -17045,7 +17045,7 @@
         <v>959</v>
       </c>
       <c r="C430" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D430" t="s">
         <v>1612</v>
@@ -17071,7 +17071,7 @@
         <v>959</v>
       </c>
       <c r="C431" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D431" t="s">
         <v>1612</v>
@@ -17123,7 +17123,7 @@
         <v>961</v>
       </c>
       <c r="C433" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D433" t="s">
         <v>1618</v>
@@ -17149,7 +17149,7 @@
         <v>959</v>
       </c>
       <c r="C434" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D434" t="s">
         <v>1618</v>
@@ -17175,7 +17175,7 @@
         <v>959</v>
       </c>
       <c r="C435" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D435" t="s">
         <v>1618</v>
@@ -17201,7 +17201,7 @@
         <v>959</v>
       </c>
       <c r="C436" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D436" t="s">
         <v>1618</v>
@@ -17253,7 +17253,7 @@
         <v>961</v>
       </c>
       <c r="C438" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D438" t="s">
         <v>1613</v>
@@ -17279,7 +17279,7 @@
         <v>961</v>
       </c>
       <c r="C439" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D439" t="s">
         <v>1613</v>
@@ -17357,7 +17357,7 @@
         <v>961</v>
       </c>
       <c r="C442" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="D442" t="s">
         <v>1615</v>
@@ -17383,7 +17383,7 @@
         <v>961</v>
       </c>
       <c r="C443" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D443" t="s">
         <v>1615</v>
@@ -17409,7 +17409,7 @@
         <v>996</v>
       </c>
       <c r="C444" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D444" t="s">
         <v>1615</v>
@@ -17487,7 +17487,7 @@
         <v>961</v>
       </c>
       <c r="C447" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="D447" t="s">
         <v>1616</v>
@@ -17513,7 +17513,7 @@
         <v>961</v>
       </c>
       <c r="C448" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D448" t="s">
         <v>1616</v>
@@ -17539,7 +17539,7 @@
         <v>996</v>
       </c>
       <c r="C449" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D449" t="s">
         <v>1616</v>
@@ -17617,7 +17617,7 @@
         <v>998</v>
       </c>
       <c r="C452" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D452" t="s">
         <v>1615</v>
@@ -17643,7 +17643,7 @@
         <v>999</v>
       </c>
       <c r="C453" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D453" t="s">
         <v>1616</v>
@@ -17669,7 +17669,7 @@
         <v>1000</v>
       </c>
       <c r="C454" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D454" t="s">
         <v>1612</v>
@@ -17695,7 +17695,7 @@
         <v>1001</v>
       </c>
       <c r="C455" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D455" t="s">
         <v>1615</v>
@@ -17721,7 +17721,7 @@
         <v>1000</v>
       </c>
       <c r="C456" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D456" t="s">
         <v>1616</v>
@@ -17773,7 +17773,7 @@
         <v>1003</v>
       </c>
       <c r="C458" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D458" t="s">
         <v>1613</v>
@@ -17799,7 +17799,7 @@
         <v>1004</v>
       </c>
       <c r="C459" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D459" t="s">
         <v>1614</v>
@@ -17851,7 +17851,7 @@
         <v>1006</v>
       </c>
       <c r="C461" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D461" t="s">
         <v>1612</v>
@@ -17877,7 +17877,7 @@
         <v>1007</v>
       </c>
       <c r="C462" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D462" t="s">
         <v>1612</v>
@@ -17929,7 +17929,7 @@
         <v>1008</v>
       </c>
       <c r="C464" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D464" t="s">
         <v>1613</v>
@@ -17955,7 +17955,7 @@
         <v>1009</v>
       </c>
       <c r="C465" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D465" t="s">
         <v>1614</v>
@@ -18085,7 +18085,7 @@
         <v>1011</v>
       </c>
       <c r="C470" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D470" t="s">
         <v>1629</v>
@@ -18111,7 +18111,7 @@
         <v>1012</v>
       </c>
       <c r="C471" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D471" t="s">
         <v>1615</v>
@@ -18137,7 +18137,7 @@
         <v>1013</v>
       </c>
       <c r="C472" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D472" t="s">
         <v>1616</v>
@@ -18189,7 +18189,7 @@
         <v>1015</v>
       </c>
       <c r="C474" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D474" t="s">
         <v>1613</v>
@@ -18215,7 +18215,7 @@
         <v>1015</v>
       </c>
       <c r="C475" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D475" t="s">
         <v>1614</v>
@@ -18241,7 +18241,7 @@
         <v>1016</v>
       </c>
       <c r="C476" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D476" t="s">
         <v>1615</v>
@@ -18267,7 +18267,7 @@
         <v>1017</v>
       </c>
       <c r="C477" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D477" t="s">
         <v>1616</v>
@@ -18293,7 +18293,7 @@
         <v>1018</v>
       </c>
       <c r="C478" t="s">
-        <v>1315</v>
+        <v>1382</v>
       </c>
       <c r="D478" t="s">
         <v>1612</v>
@@ -18319,7 +18319,7 @@
         <v>1019</v>
       </c>
       <c r="C479" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D479" t="s">
         <v>1618</v>
@@ -18345,7 +18345,7 @@
         <v>1020</v>
       </c>
       <c r="C480" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D480" t="s">
         <v>1618</v>
@@ -18371,7 +18371,7 @@
         <v>1021</v>
       </c>
       <c r="C481" t="s">
-        <v>1315</v>
+        <v>1382</v>
       </c>
       <c r="D481" t="s">
         <v>1615</v>
@@ -18397,7 +18397,7 @@
         <v>1018</v>
       </c>
       <c r="C482" t="s">
-        <v>1315</v>
+        <v>1382</v>
       </c>
       <c r="D482" t="s">
         <v>1616</v>
@@ -18449,7 +18449,7 @@
         <v>1023</v>
       </c>
       <c r="C484" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D484" t="s">
         <v>1613</v>
@@ -18475,7 +18475,7 @@
         <v>1024</v>
       </c>
       <c r="C485" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D485" t="s">
         <v>1614</v>
@@ -18631,7 +18631,7 @@
         <v>1027</v>
       </c>
       <c r="C491" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D491" t="s">
         <v>1613</v>
@@ -18657,7 +18657,7 @@
         <v>1028</v>
       </c>
       <c r="C492" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D492" t="s">
         <v>1614</v>
@@ -18683,7 +18683,7 @@
         <v>1029</v>
       </c>
       <c r="C493" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D493" t="s">
         <v>1615</v>
@@ -18709,7 +18709,7 @@
         <v>1030</v>
       </c>
       <c r="C494" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D494" t="s">
         <v>1616</v>
@@ -18839,7 +18839,7 @@
         <v>961</v>
       </c>
       <c r="C499" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D499" t="s">
         <v>1614</v>
@@ -19307,7 +19307,7 @@
         <v>958</v>
       </c>
       <c r="C517" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D517" t="s">
         <v>1612</v>
@@ -19333,7 +19333,7 @@
         <v>961</v>
       </c>
       <c r="C518" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D518" t="s">
         <v>1613</v>
@@ -19359,7 +19359,7 @@
         <v>961</v>
       </c>
       <c r="C519" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D519" t="s">
         <v>1614</v>
@@ -19567,7 +19567,7 @@
         <v>961</v>
       </c>
       <c r="C527" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D527" t="s">
         <v>1614</v>
@@ -20347,7 +20347,7 @@
         <v>958</v>
       </c>
       <c r="C557" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D557" t="s">
         <v>1612</v>
@@ -20789,7 +20789,7 @@
         <v>1043</v>
       </c>
       <c r="C574" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D574" t="s">
         <v>1612</v>
@@ -21127,7 +21127,7 @@
         <v>1054</v>
       </c>
       <c r="C587" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D587" t="s">
         <v>1612</v>
@@ -21153,7 +21153,7 @@
         <v>1055</v>
       </c>
       <c r="C588" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D588" t="s">
         <v>1615</v>
@@ -21179,7 +21179,7 @@
         <v>1056</v>
       </c>
       <c r="C589" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D589" t="s">
         <v>1616</v>
@@ -21231,7 +21231,7 @@
         <v>1058</v>
       </c>
       <c r="C591" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D591" t="s">
         <v>1612</v>
@@ -21309,7 +21309,7 @@
         <v>1058</v>
       </c>
       <c r="C594" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D594" t="s">
         <v>1616</v>
@@ -21439,7 +21439,7 @@
         <v>1064</v>
       </c>
       <c r="C599" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D599" t="s">
         <v>1612</v>
@@ -21621,7 +21621,7 @@
         <v>1064</v>
       </c>
       <c r="C606" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D606" t="s">
         <v>1616</v>
@@ -21699,7 +21699,7 @@
         <v>1068</v>
       </c>
       <c r="C609" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D609" t="s">
         <v>1612</v>
@@ -21751,7 +21751,7 @@
         <v>1070</v>
       </c>
       <c r="C611" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D611" t="s">
         <v>1616</v>
@@ -21777,7 +21777,7 @@
         <v>961</v>
       </c>
       <c r="C612" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D612" t="s">
         <v>1612</v>
@@ -21803,7 +21803,7 @@
         <v>961</v>
       </c>
       <c r="C613" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D613" t="s">
         <v>1612</v>
@@ -21907,7 +21907,7 @@
         <v>959</v>
       </c>
       <c r="C617" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D617" t="s">
         <v>1613</v>
@@ -22063,7 +22063,7 @@
         <v>958</v>
       </c>
       <c r="C623" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D623" t="s">
         <v>1615</v>
@@ -22141,7 +22141,7 @@
         <v>961</v>
       </c>
       <c r="C626" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D626" t="s">
         <v>1616</v>
@@ -22167,7 +22167,7 @@
         <v>961</v>
       </c>
       <c r="C627" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D627" t="s">
         <v>1612</v>
@@ -22271,7 +22271,7 @@
         <v>958</v>
       </c>
       <c r="C631" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D631" t="s">
         <v>1615</v>
@@ -22505,7 +22505,7 @@
         <v>959</v>
       </c>
       <c r="C640" t="s">
-        <v>1332</v>
+        <v>1315</v>
       </c>
       <c r="D640" t="s">
         <v>1614</v>
@@ -22583,7 +22583,7 @@
         <v>958</v>
       </c>
       <c r="C643" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D643" t="s">
         <v>1612</v>
@@ -22661,7 +22661,7 @@
         <v>959</v>
       </c>
       <c r="C646" t="s">
-        <v>1332</v>
+        <v>1315</v>
       </c>
       <c r="D646" t="s">
         <v>1613</v>
@@ -22739,7 +22739,7 @@
         <v>961</v>
       </c>
       <c r="C649" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D649" t="s">
         <v>1616</v>
@@ -25391,7 +25391,7 @@
         <v>1082</v>
       </c>
       <c r="C751" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D751" t="s">
         <v>1615</v>
@@ -25833,7 +25833,7 @@
         <v>1095</v>
       </c>
       <c r="C768" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D768" t="s">
         <v>1619</v>
@@ -25859,7 +25859,7 @@
         <v>959</v>
       </c>
       <c r="C769" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D769" t="s">
         <v>1616</v>
@@ -25911,7 +25911,7 @@
         <v>959</v>
       </c>
       <c r="C771" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D771" t="s">
         <v>1615</v>
@@ -25937,7 +25937,7 @@
         <v>961</v>
       </c>
       <c r="C772" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D772" t="s">
         <v>1612</v>
@@ -26015,7 +26015,7 @@
         <v>1098</v>
       </c>
       <c r="C775" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D775" t="s">
         <v>1620</v>
@@ -26041,7 +26041,7 @@
         <v>961</v>
       </c>
       <c r="C776" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D776" t="s">
         <v>1612</v>
@@ -26067,7 +26067,7 @@
         <v>1099</v>
       </c>
       <c r="C777" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D777" t="s">
         <v>1619</v>
@@ -26119,7 +26119,7 @@
         <v>1100</v>
       </c>
       <c r="C779" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D779" t="s">
         <v>1612</v>
@@ -26327,7 +26327,7 @@
         <v>1107</v>
       </c>
       <c r="C787" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D787" t="s">
         <v>1615</v>
@@ -26665,7 +26665,7 @@
         <v>1115</v>
       </c>
       <c r="C800" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D800" t="s">
         <v>1615</v>
@@ -26717,7 +26717,7 @@
         <v>1115</v>
       </c>
       <c r="C802" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D802" t="s">
         <v>1616</v>
@@ -26899,7 +26899,7 @@
         <v>1120</v>
       </c>
       <c r="C809" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D809" t="s">
         <v>1619</v>
@@ -27029,7 +27029,7 @@
         <v>961</v>
       </c>
       <c r="C814" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D814" t="s">
         <v>1612</v>
@@ -27055,7 +27055,7 @@
         <v>1124</v>
       </c>
       <c r="C815" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D815" t="s">
         <v>1621</v>
@@ -27107,7 +27107,7 @@
         <v>1125</v>
       </c>
       <c r="C817" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D817" t="s">
         <v>1620</v>
@@ -27133,7 +27133,7 @@
         <v>961</v>
       </c>
       <c r="C818" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D818" t="s">
         <v>1612</v>
@@ -27185,7 +27185,7 @@
         <v>1127</v>
       </c>
       <c r="C820" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D820" t="s">
         <v>1619</v>
@@ -28667,7 +28667,7 @@
         <v>961</v>
       </c>
       <c r="C877" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D877" t="s">
         <v>1616</v>
@@ -28719,7 +28719,7 @@
         <v>1132</v>
       </c>
       <c r="C879" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D879" t="s">
         <v>1622</v>
@@ -28745,7 +28745,7 @@
         <v>1132</v>
       </c>
       <c r="C880" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D880" t="s">
         <v>1621</v>
@@ -28823,7 +28823,7 @@
         <v>958</v>
       </c>
       <c r="C883" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D883" t="s">
         <v>1612</v>
@@ -28901,7 +28901,7 @@
         <v>1135</v>
       </c>
       <c r="C886" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D886" t="s">
         <v>1619</v>
@@ -28927,7 +28927,7 @@
         <v>1136</v>
       </c>
       <c r="C887" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D887" t="s">
         <v>1620</v>
@@ -28979,7 +28979,7 @@
         <v>959</v>
       </c>
       <c r="C889" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D889" t="s">
         <v>1613</v>
@@ -29031,7 +29031,7 @@
         <v>959</v>
       </c>
       <c r="C891" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D891" t="s">
         <v>1614</v>
@@ -29109,7 +29109,7 @@
         <v>961</v>
       </c>
       <c r="C894" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D894" t="s">
         <v>1616</v>
@@ -29525,7 +29525,7 @@
         <v>1074</v>
       </c>
       <c r="C910" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D910" t="s">
         <v>1612</v>
@@ -29863,7 +29863,7 @@
         <v>959</v>
       </c>
       <c r="C923" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D923" t="s">
         <v>1616</v>
@@ -29889,7 +29889,7 @@
         <v>1145</v>
       </c>
       <c r="C924" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D924" t="s">
         <v>1613</v>
@@ -29941,7 +29941,7 @@
         <v>961</v>
       </c>
       <c r="C926" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D926" t="s">
         <v>1615</v>
@@ -29967,7 +29967,7 @@
         <v>1146</v>
       </c>
       <c r="C927" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D927" t="s">
         <v>1620</v>
@@ -30019,7 +30019,7 @@
         <v>1148</v>
       </c>
       <c r="C929" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D929" t="s">
         <v>1619</v>
@@ -30045,7 +30045,7 @@
         <v>961</v>
       </c>
       <c r="C930" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D930" t="s">
         <v>1616</v>
@@ -30253,7 +30253,7 @@
         <v>1074</v>
       </c>
       <c r="C938" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D938" t="s">
         <v>1613</v>
@@ -30279,7 +30279,7 @@
         <v>961</v>
       </c>
       <c r="C939" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D939" t="s">
         <v>1614</v>
@@ -30877,7 +30877,7 @@
         <v>959</v>
       </c>
       <c r="C962" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D962" t="s">
         <v>1616</v>
@@ -30929,7 +30929,7 @@
         <v>1155</v>
       </c>
       <c r="C964" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D964" t="s">
         <v>1622</v>
@@ -30981,7 +30981,7 @@
         <v>961</v>
       </c>
       <c r="C966" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D966" t="s">
         <v>1615</v>
@@ -31007,7 +31007,7 @@
         <v>1156</v>
       </c>
       <c r="C967" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D967" t="s">
         <v>1620</v>
@@ -31033,7 +31033,7 @@
         <v>1157</v>
       </c>
       <c r="C968" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D968" t="s">
         <v>1619</v>
@@ -31059,7 +31059,7 @@
         <v>961</v>
       </c>
       <c r="C969" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D969" t="s">
         <v>1616</v>
@@ -31657,7 +31657,7 @@
         <v>958</v>
       </c>
       <c r="C992" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D992" t="s">
         <v>1612</v>
@@ -31683,7 +31683,7 @@
         <v>959</v>
       </c>
       <c r="C993" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D993" t="s">
         <v>1613</v>
@@ -31709,7 +31709,7 @@
         <v>959</v>
       </c>
       <c r="C994" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D994" t="s">
         <v>1614</v>
@@ -31839,7 +31839,7 @@
         <v>958</v>
       </c>
       <c r="C999" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D999" t="s">
         <v>1612</v>
@@ -31865,7 +31865,7 @@
         <v>959</v>
       </c>
       <c r="C1000" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1000" t="s">
         <v>1613</v>
@@ -31917,7 +31917,7 @@
         <v>959</v>
       </c>
       <c r="C1002" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1002" t="s">
         <v>1614</v>
@@ -32853,7 +32853,7 @@
         <v>959</v>
       </c>
       <c r="C1038" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1038" t="s">
         <v>1613</v>
@@ -32879,7 +32879,7 @@
         <v>959</v>
       </c>
       <c r="C1039" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D1039" t="s">
         <v>1615</v>
@@ -32931,7 +32931,7 @@
         <v>958</v>
       </c>
       <c r="C1041" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1041" t="s">
         <v>1612</v>
@@ -32957,7 +32957,7 @@
         <v>958</v>
       </c>
       <c r="C1042" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1042" t="s">
         <v>1615</v>
@@ -33243,7 +33243,7 @@
         <v>959</v>
       </c>
       <c r="C1053" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1053" t="s">
         <v>1612</v>
@@ -33451,7 +33451,7 @@
         <v>1183</v>
       </c>
       <c r="C1061" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D1061" t="s">
         <v>1613</v>
@@ -33841,7 +33841,7 @@
         <v>1193</v>
       </c>
       <c r="C1076" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D1076" t="s">
         <v>1617</v>
@@ -33867,7 +33867,7 @@
         <v>958</v>
       </c>
       <c r="C1077" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1077" t="s">
         <v>1613</v>
@@ -33893,7 +33893,7 @@
         <v>961</v>
       </c>
       <c r="C1078" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1078" t="s">
         <v>1614</v>
@@ -33945,7 +33945,7 @@
         <v>1194</v>
       </c>
       <c r="C1080" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D1080" t="s">
         <v>1620</v>
@@ -33971,7 +33971,7 @@
         <v>958</v>
       </c>
       <c r="C1081" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1081" t="s">
         <v>1612</v>
@@ -33997,7 +33997,7 @@
         <v>958</v>
       </c>
       <c r="C1082" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1082" t="s">
         <v>1615</v>
@@ -34049,7 +34049,7 @@
         <v>959</v>
       </c>
       <c r="C1084" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D1084" t="s">
         <v>1613</v>
@@ -34205,7 +34205,7 @@
         <v>959</v>
       </c>
       <c r="C1090" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1090" t="s">
         <v>1613</v>
@@ -35375,7 +35375,7 @@
         <v>961</v>
       </c>
       <c r="C1135" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D1135" t="s">
         <v>1612</v>
@@ -35401,7 +35401,7 @@
         <v>958</v>
       </c>
       <c r="C1136" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1136" t="s">
         <v>1615</v>
@@ -35427,7 +35427,7 @@
         <v>1198</v>
       </c>
       <c r="C1137" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D1137" t="s">
         <v>1616</v>
@@ -35453,7 +35453,7 @@
         <v>958</v>
       </c>
       <c r="C1138" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1138" t="s">
         <v>1612</v>
@@ -35479,7 +35479,7 @@
         <v>958</v>
       </c>
       <c r="C1139" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1139" t="s">
         <v>1615</v>
@@ -35505,7 +35505,7 @@
         <v>1199</v>
       </c>
       <c r="C1140" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1140" t="s">
         <v>1617</v>
@@ -35531,7 +35531,7 @@
         <v>1200</v>
       </c>
       <c r="C1141" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1141" t="s">
         <v>1613</v>
@@ -35557,7 +35557,7 @@
         <v>1201</v>
       </c>
       <c r="C1142" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1142" t="s">
         <v>1614</v>
@@ -35609,7 +35609,7 @@
         <v>1203</v>
       </c>
       <c r="C1144" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D1144" t="s">
         <v>1617</v>
@@ -35635,7 +35635,7 @@
         <v>959</v>
       </c>
       <c r="C1145" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1145" t="s">
         <v>1613</v>
@@ -35661,7 +35661,7 @@
         <v>958</v>
       </c>
       <c r="C1146" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1146" t="s">
         <v>1615</v>
@@ -35687,7 +35687,7 @@
         <v>1204</v>
       </c>
       <c r="C1147" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D1147" t="s">
         <v>1620</v>
@@ -35765,7 +35765,7 @@
         <v>1205</v>
       </c>
       <c r="C1150" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1150" t="s">
         <v>1613</v>
@@ -35791,7 +35791,7 @@
         <v>1206</v>
       </c>
       <c r="C1151" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D1151" t="s">
         <v>1613</v>
@@ -35817,7 +35817,7 @@
         <v>1205</v>
       </c>
       <c r="C1152" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1152" t="s">
         <v>1614</v>
@@ -35843,7 +35843,7 @@
         <v>1206</v>
       </c>
       <c r="C1153" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D1153" t="s">
         <v>1614</v>
@@ -36077,7 +36077,7 @@
         <v>958</v>
       </c>
       <c r="C1162" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1162" t="s">
         <v>1612</v>
@@ -36103,7 +36103,7 @@
         <v>958</v>
       </c>
       <c r="C1163" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1163" t="s">
         <v>1615</v>
@@ -36155,7 +36155,7 @@
         <v>1213</v>
       </c>
       <c r="C1165" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D1165" t="s">
         <v>1622</v>
@@ -36181,7 +36181,7 @@
         <v>1214</v>
       </c>
       <c r="C1166" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D1166" t="s">
         <v>1621</v>
@@ -36233,7 +36233,7 @@
         <v>958</v>
       </c>
       <c r="C1168" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D1168" t="s">
         <v>1612</v>
@@ -36259,7 +36259,7 @@
         <v>959</v>
       </c>
       <c r="C1169" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1169" t="s">
         <v>1613</v>
@@ -36337,7 +36337,7 @@
         <v>1218</v>
       </c>
       <c r="C1172" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D1172" t="s">
         <v>1622</v>
@@ -36961,7 +36961,7 @@
         <v>1220</v>
       </c>
       <c r="C1196" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D1196" t="s">
         <v>1622</v>
@@ -36987,7 +36987,7 @@
         <v>958</v>
       </c>
       <c r="C1197" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1197" t="s">
         <v>1615</v>
@@ -37013,7 +37013,7 @@
         <v>1221</v>
       </c>
       <c r="C1198" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1198" t="s">
         <v>1620</v>
@@ -37039,7 +37039,7 @@
         <v>958</v>
       </c>
       <c r="C1199" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1199" t="s">
         <v>1612</v>
@@ -37065,7 +37065,7 @@
         <v>958</v>
       </c>
       <c r="C1200" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1200" t="s">
         <v>1615</v>
@@ -37091,7 +37091,7 @@
         <v>958</v>
       </c>
       <c r="C1201" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1201" t="s">
         <v>1613</v>
@@ -37117,7 +37117,7 @@
         <v>961</v>
       </c>
       <c r="C1202" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1202" t="s">
         <v>1614</v>
@@ -37143,7 +37143,7 @@
         <v>959</v>
       </c>
       <c r="C1203" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D1203" t="s">
         <v>1615</v>
@@ -37169,7 +37169,7 @@
         <v>1222</v>
       </c>
       <c r="C1204" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1204" t="s">
         <v>1620</v>
@@ -37195,7 +37195,7 @@
         <v>961</v>
       </c>
       <c r="C1205" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1205" t="s">
         <v>1612</v>
@@ -37221,7 +37221,7 @@
         <v>961</v>
       </c>
       <c r="C1206" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D1206" t="s">
         <v>1613</v>
@@ -37247,7 +37247,7 @@
         <v>958</v>
       </c>
       <c r="C1207" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="D1207" t="s">
         <v>1615</v>
@@ -37273,7 +37273,7 @@
         <v>958</v>
       </c>
       <c r="C1208" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1208" t="s">
         <v>1616</v>
@@ -37299,7 +37299,7 @@
         <v>1223</v>
       </c>
       <c r="C1209" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1209" t="s">
         <v>1617</v>
@@ -37325,7 +37325,7 @@
         <v>959</v>
       </c>
       <c r="C1210" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1210" t="s">
         <v>1613</v>
@@ -37351,7 +37351,7 @@
         <v>1224</v>
       </c>
       <c r="C1211" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D1211" t="s">
         <v>1619</v>
@@ -37377,7 +37377,7 @@
         <v>961</v>
       </c>
       <c r="C1212" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D1212" t="s">
         <v>1616</v>
@@ -37429,7 +37429,7 @@
         <v>958</v>
       </c>
       <c r="C1214" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1214" t="s">
         <v>1615</v>
@@ -37455,7 +37455,7 @@
         <v>961</v>
       </c>
       <c r="C1215" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1215" t="s">
         <v>1616</v>
@@ -42135,7 +42135,7 @@
         <v>958</v>
       </c>
       <c r="C1395" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D1395" t="s">
         <v>1612</v>
@@ -42499,7 +42499,7 @@
         <v>958</v>
       </c>
       <c r="C1409" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D1409" t="s">
         <v>1615</v>
@@ -42603,7 +42603,7 @@
         <v>1225</v>
       </c>
       <c r="C1413" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D1413" t="s">
         <v>1612</v>
@@ -42811,7 +42811,7 @@
         <v>1230</v>
       </c>
       <c r="C1421" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1421" t="s">
         <v>1613</v>
@@ -42915,7 +42915,7 @@
         <v>1230</v>
       </c>
       <c r="C1425" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1425" t="s">
         <v>1614</v>
@@ -43253,7 +43253,7 @@
         <v>1225</v>
       </c>
       <c r="C1438" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D1438" t="s">
         <v>1615</v>
@@ -44969,7 +44969,7 @@
         <v>961</v>
       </c>
       <c r="C1504" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1504" t="s">
         <v>1612</v>
@@ -45151,7 +45151,7 @@
         <v>961</v>
       </c>
       <c r="C1511" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1511" t="s">
         <v>1616</v>
@@ -45229,7 +45229,7 @@
         <v>959</v>
       </c>
       <c r="C1514" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1514" t="s">
         <v>1612</v>
@@ -45255,7 +45255,7 @@
         <v>959</v>
       </c>
       <c r="C1515" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1515" t="s">
         <v>1612</v>
@@ -45281,7 +45281,7 @@
         <v>959</v>
       </c>
       <c r="C1516" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1516" t="s">
         <v>1618</v>
@@ -45307,7 +45307,7 @@
         <v>959</v>
       </c>
       <c r="C1517" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1517" t="s">
         <v>1613</v>
@@ -45359,7 +45359,7 @@
         <v>959</v>
       </c>
       <c r="C1519" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1519" t="s">
         <v>1616</v>
@@ -45385,7 +45385,7 @@
         <v>961</v>
       </c>
       <c r="C1520" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1520" t="s">
         <v>1612</v>
@@ -45515,7 +45515,7 @@
         <v>958</v>
       </c>
       <c r="C1525" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D1525" t="s">
         <v>1613</v>
@@ -45645,7 +45645,7 @@
         <v>959</v>
       </c>
       <c r="C1530" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1530" t="s">
         <v>1618</v>
@@ -45775,7 +45775,7 @@
         <v>958</v>
       </c>
       <c r="C1535" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D1535" t="s">
         <v>1615</v>
@@ -45905,7 +45905,7 @@
         <v>959</v>
       </c>
       <c r="C1540" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1540" t="s">
         <v>1618</v>
@@ -45957,7 +45957,7 @@
         <v>959</v>
       </c>
       <c r="C1542" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1542" t="s">
         <v>1613</v>
@@ -46087,7 +46087,7 @@
         <v>959</v>
       </c>
       <c r="C1547" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1547" t="s">
         <v>1614</v>
@@ -46243,7 +46243,7 @@
         <v>959</v>
       </c>
       <c r="C1553" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D1553" t="s">
         <v>1616</v>
@@ -47361,7 +47361,7 @@
         <v>959</v>
       </c>
       <c r="C1596" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D1596" t="s">
         <v>1634</v>
